--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5081"/>
+  <dimension ref="A1:C5087"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86795,6 +86795,108 @@
       <c r="C5081" t="inlineStr">
         <is>
           <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5082">
+      <c r="A5082" t="inlineStr">
+        <is>
+          <t>85171</t>
+        </is>
+      </c>
+      <c r="B5082" t="inlineStr">
+        <is>
+          <t>OUI VELUD ACET HID CPO MON AMIE 037 200g</t>
+        </is>
+      </c>
+      <c r="C5082" t="inlineStr">
+        <is>
+          <t>O.U.I</t>
+        </is>
+      </c>
+    </row>
+    <row r="5083">
+      <c r="A5083" t="inlineStr">
+        <is>
+          <t>95687</t>
+        </is>
+      </c>
+      <c r="B5083" t="inlineStr">
+        <is>
+          <t>Presente Neo Hidramineral</t>
+        </is>
+      </c>
+      <c r="C5083" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5084">
+      <c r="A5084" t="inlineStr">
+        <is>
+          <t>87478</t>
+        </is>
+      </c>
+      <c r="B5084" t="inlineStr">
+        <is>
+          <t>BOTIK GEL LIMP FAC VITAM C V2 200g</t>
+        </is>
+      </c>
+      <c r="C5084" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5085">
+      <c r="A5085" t="inlineStr">
+        <is>
+          <t>88101</t>
+        </is>
+      </c>
+      <c r="B5085" t="inlineStr">
+        <is>
+          <t>QDB LIP TINT CEREJA PROFUNDO 4ml</t>
+        </is>
+      </c>
+      <c r="C5085" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="5086">
+      <c r="A5086" t="inlineStr">
+        <is>
+          <t>90611</t>
+        </is>
+      </c>
+      <c r="B5086" t="inlineStr">
+        <is>
+          <t>BOTICÁRIO MEN GEL SECATIVO ANTIACNE, 15g</t>
+        </is>
+      </c>
+      <c r="C5086" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5087">
+      <c r="A5087" t="inlineStr">
+        <is>
+          <t>86226</t>
+        </is>
+      </c>
+      <c r="B5087" t="inlineStr">
+        <is>
+          <t>INSTANCE CR HID MAOS BAUN/INTENSA 30g</t>
+        </is>
+      </c>
+      <c r="C5087" t="inlineStr">
+        <is>
+          <t>Eudora</t>
         </is>
       </c>
     </row>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5087"/>
+  <dimension ref="A1:C5092"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86897,6 +86897,91 @@
       <c r="C5087" t="inlineStr">
         <is>
           <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5088">
+      <c r="A5088" t="inlineStr">
+        <is>
+          <t>94859</t>
+        </is>
+      </c>
+      <c r="B5088" t="inlineStr">
+        <is>
+          <t>HER CODE LOC DES HID CPO V2 200ml</t>
+        </is>
+      </c>
+      <c r="C5088" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5089">
+      <c r="A5089" t="inlineStr">
+        <is>
+          <t>85482</t>
+        </is>
+      </c>
+      <c r="B5089" t="inlineStr">
+        <is>
+          <t>FLORATTA DES BDY SPR F/SECRET V2 100ml</t>
+        </is>
+      </c>
+      <c r="C5089" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5090">
+      <c r="A5090" t="inlineStr">
+        <is>
+          <t>88690</t>
+        </is>
+      </c>
+      <c r="B5090" t="inlineStr">
+        <is>
+          <t>REF CBEM LOC D H CP NUVEM N/FORM 350ml</t>
+        </is>
+      </c>
+      <c r="C5090" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5091">
+      <c r="A5091" t="inlineStr">
+        <is>
+          <t>87914</t>
+        </is>
+      </c>
+      <c r="B5091" t="inlineStr">
+        <is>
+          <t>NSPA CREM HID MAOS/PES LILAC V2 50g</t>
+        </is>
+      </c>
+      <c r="C5091" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5092">
+      <c r="A5092" t="inlineStr">
+        <is>
+          <t>46895</t>
+        </is>
+      </c>
+      <c r="B5092" t="inlineStr">
+        <is>
+          <t>BOTI MASSAG CPO PP</t>
+        </is>
+      </c>
+      <c r="C5092" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
         </is>
       </c>
     </row>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5092"/>
+  <dimension ref="A1:C5097"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86982,6 +86982,91 @@
       <c r="C5092" t="inlineStr">
         <is>
           <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5093">
+      <c r="A5093" t="inlineStr">
+        <is>
+          <t>87779</t>
+        </is>
+      </c>
+      <c r="B5093" t="inlineStr">
+        <is>
+          <t>INSTANCE REFIL CREME HIDRATANTE DESODORANTE CORPORAL BAUNILHA INTENSA 400ml</t>
+        </is>
+      </c>
+      <c r="C5093" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5094">
+      <c r="A5094" t="inlineStr">
+        <is>
+          <t>96307</t>
+        </is>
+      </c>
+      <c r="B5094" t="inlineStr">
+        <is>
+          <t>COMB EGEO VANILLA VIBE</t>
+        </is>
+      </c>
+      <c r="C5094" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5095">
+      <c r="A5095" t="inlineStr">
+        <is>
+          <t>95688</t>
+        </is>
+      </c>
+      <c r="B5095" t="inlineStr">
+        <is>
+          <t>Presente Neo Colágeno</t>
+        </is>
+      </c>
+      <c r="C5095" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5096">
+      <c r="A5096" t="inlineStr">
+        <is>
+          <t>88395</t>
+        </is>
+      </c>
+      <c r="B5096" t="inlineStr">
+        <is>
+          <t>CBEM DES COL BDY SPLSH ROS/ALG V4 200ml</t>
+        </is>
+      </c>
+      <c r="C5096" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5097">
+      <c r="A5097" t="inlineStr">
+        <is>
+          <t>86031</t>
+        </is>
+      </c>
+      <c r="B5097" t="inlineStr">
+        <is>
+          <t>INSTANCE DES ANT ROLL FR/VERM V2 55ml</t>
+        </is>
+      </c>
+      <c r="C5097" t="inlineStr">
+        <is>
+          <t>Eudora</t>
         </is>
       </c>
     </row>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5097"/>
+  <dimension ref="A1:C5098"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87067,6 +87067,23 @@
       <c r="C5097" t="inlineStr">
         <is>
           <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5098">
+      <c r="A5098" t="inlineStr">
+        <is>
+          <t>83784</t>
+        </is>
+      </c>
+      <c r="B5098" t="inlineStr">
+        <is>
+          <t>DEM FLORATTA DES COL SPLASH BLUE 4ml</t>
+        </is>
+      </c>
+      <c r="C5098" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
         </is>
       </c>
     </row>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5098"/>
+  <dimension ref="A1:C5108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87084,6 +87084,176 @@
       <c r="C5098" t="inlineStr">
         <is>
           <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5099">
+      <c r="A5099" t="inlineStr">
+        <is>
+          <t>85899</t>
+        </is>
+      </c>
+      <c r="B5099" t="inlineStr">
+        <is>
+          <t>PULSE DESODORANTE COLONIA INTENSE 100ml</t>
+        </is>
+      </c>
+      <c r="C5099" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5100">
+      <c r="A5100" t="inlineStr">
+        <is>
+          <t>86713</t>
+        </is>
+      </c>
+      <c r="B5100" t="inlineStr">
+        <is>
+          <t>PULSE INTENSE SHOWER GEL CABELO E CORPO, 100g</t>
+        </is>
+      </c>
+      <c r="C5100" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5101">
+      <c r="A5101" t="inlineStr">
+        <is>
+          <t>90189</t>
+        </is>
+      </c>
+      <c r="B5101" t="inlineStr">
+        <is>
+          <t>COMBO INSTANCE KARITÉ COM ATÉ 41% DE DESCONTO</t>
+        </is>
+      </c>
+      <c r="C5101" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5102">
+      <c r="A5102" t="inlineStr">
+        <is>
+          <t>89635</t>
+        </is>
+      </c>
+      <c r="B5102" t="inlineStr">
+        <is>
+          <t>KIT MINI ESPONJA BLEND PERFECTION</t>
+        </is>
+      </c>
+      <c r="C5102" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5103">
+      <c r="A5103" t="inlineStr">
+        <is>
+          <t>96053</t>
+        </is>
+      </c>
+      <c r="B5103" t="inlineStr">
+        <is>
+          <t>COMB PULSE 03</t>
+        </is>
+      </c>
+      <c r="C5103" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5104">
+      <c r="A5104" t="inlineStr">
+        <is>
+          <t>90745</t>
+        </is>
+      </c>
+      <c r="B5104" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ TO NO GLOW 280Q V2 30ml</t>
+        </is>
+      </c>
+      <c r="C5104" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="5105">
+      <c r="A5105" t="inlineStr">
+        <is>
+          <t>94230</t>
+        </is>
+      </c>
+      <c r="B5105" t="inlineStr">
+        <is>
+          <t>EUDORA MAKE CORRETIVO LÍQUIDO SKIN PERFECTION COR 270Q 4ml</t>
+        </is>
+      </c>
+      <c r="C5105" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5106">
+      <c r="A5106" t="inlineStr">
+        <is>
+          <t>94221</t>
+        </is>
+      </c>
+      <c r="B5106" t="inlineStr">
+        <is>
+          <t>EUDORA MAKE CORRETIVO LÍQUIDO SKIN PERFECTION COR 150N 4ml</t>
+        </is>
+      </c>
+      <c r="C5106" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5107">
+      <c r="A5107" t="inlineStr">
+        <is>
+          <t>89493</t>
+        </is>
+      </c>
+      <c r="B5107" t="inlineStr">
+        <is>
+          <t>MEN LOC DES HID CPO V2 200ml</t>
+        </is>
+      </c>
+      <c r="C5107" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5108">
+      <c r="A5108" t="inlineStr">
+        <is>
+          <t>86121</t>
+        </is>
+      </c>
+      <c r="B5108" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ POP 120N 30ml</t>
+        </is>
+      </c>
+      <c r="C5108" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
         </is>
       </c>
     </row>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5108"/>
+  <dimension ref="A1:C5118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87254,6 +87254,176 @@
       <c r="C5108" t="inlineStr">
         <is>
           <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="5109">
+      <c r="A5109" t="inlineStr">
+        <is>
+          <t>95905</t>
+        </is>
+      </c>
+      <c r="B5109" t="inlineStr">
+        <is>
+          <t>Presente Lyra Happy</t>
+        </is>
+      </c>
+      <c r="C5109" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5110">
+      <c r="A5110" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B5110" t="inlineStr">
+        <is>
+          <t>Combo Boti Baby (3 itens)</t>
+        </is>
+      </c>
+      <c r="C5110" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5111">
+      <c r="A5111" t="inlineStr">
+        <is>
+          <t>95656</t>
+        </is>
+      </c>
+      <c r="B5111" t="inlineStr">
+        <is>
+          <t>Presente Velvet Inspire</t>
+        </is>
+      </c>
+      <c r="C5111" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5112">
+      <c r="A5112" t="inlineStr">
+        <is>
+          <t>88103</t>
+        </is>
+      </c>
+      <c r="B5112" t="inlineStr">
+        <is>
+          <t>QDB LIP TINT PESSEGO SUAVE 4ml</t>
+        </is>
+      </c>
+      <c r="C5112" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="5113">
+      <c r="A5113" t="inlineStr">
+        <is>
+          <t>94610</t>
+        </is>
+      </c>
+      <c r="B5113" t="inlineStr">
+        <is>
+          <t>NSPA DES COL BDY/SPL ORQ/NOIRE V2 200ml</t>
+        </is>
+      </c>
+      <c r="C5113" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5114">
+      <c r="A5114" t="inlineStr">
+        <is>
+          <t>85007</t>
+        </is>
+      </c>
+      <c r="B5114" t="inlineStr">
+        <is>
+          <t>EUD MAKE BASE LIQUIDA SKIN PERFECTION 140Q</t>
+        </is>
+      </c>
+      <c r="C5114" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5115">
+      <c r="A5115" t="inlineStr">
+        <is>
+          <t>88696</t>
+        </is>
+      </c>
+      <c r="B5115" t="inlineStr">
+        <is>
+          <t>REF CBEM LOC D H CP R/ALG N/FORM 350ml</t>
+        </is>
+      </c>
+      <c r="C5115" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5116">
+      <c r="A5116" t="inlineStr">
+        <is>
+          <t>94226</t>
+        </is>
+      </c>
+      <c r="B5116" t="inlineStr">
+        <is>
+          <t>EUDORA MAKE CORRETIVO LÍQUIDO SKIN PERFECTION COR 210Q 4ml</t>
+        </is>
+      </c>
+      <c r="C5116" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5117">
+      <c r="A5117" t="inlineStr">
+        <is>
+          <t>93108</t>
+        </is>
+      </c>
+      <c r="B5117" t="inlineStr">
+        <is>
+          <t>SCH LA PIEL LOC D H CPO AMB/DOUR 7ml VDA</t>
+        </is>
+      </c>
+      <c r="C5117" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5118">
+      <c r="A5118" t="inlineStr">
+        <is>
+          <t>93752</t>
+        </is>
+      </c>
+      <c r="B5118" t="inlineStr">
+        <is>
+          <t>SCH LA PIEL LOC DES H CP CRI/HIM 7ml VDA</t>
+        </is>
+      </c>
+      <c r="C5118" t="inlineStr">
+        <is>
+          <t>Eudora</t>
         </is>
       </c>
     </row>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5118"/>
+  <dimension ref="A1:C5124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87422,6 +87422,108 @@
         </is>
       </c>
       <c r="C5118" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5119">
+      <c r="A5119" t="inlineStr">
+        <is>
+          <t>85011</t>
+        </is>
+      </c>
+      <c r="B5119" t="inlineStr">
+        <is>
+          <t>EUD MAKE BASE LIQUIDA SKIN PERFECTION 120N</t>
+        </is>
+      </c>
+      <c r="C5119" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5120">
+      <c r="A5120" t="inlineStr">
+        <is>
+          <t>96051</t>
+        </is>
+      </c>
+      <c r="B5120" t="inlineStr">
+        <is>
+          <t>COMBO NIINA MOUSSE DE LIMPEZA + SORBET</t>
+        </is>
+      </c>
+      <c r="C5120" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5121">
+      <c r="A5121" t="inlineStr">
+        <is>
+          <t>85013</t>
+        </is>
+      </c>
+      <c r="B5121" t="inlineStr">
+        <is>
+          <t>EUD MAKE BASE LIQUIDA SKIN PERFECTION 185Q</t>
+        </is>
+      </c>
+      <c r="C5121" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5122">
+      <c r="A5122" t="inlineStr">
+        <is>
+          <t>85014</t>
+        </is>
+      </c>
+      <c r="B5122" t="inlineStr">
+        <is>
+          <t>EUDORA MAKE BASE LIQUIDA MATTE SKIN PERFECTION 200Q 30ml</t>
+        </is>
+      </c>
+      <c r="C5122" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5123">
+      <c r="A5123" t="inlineStr">
+        <is>
+          <t>85315</t>
+        </is>
+      </c>
+      <c r="B5123" t="inlineStr">
+        <is>
+          <t>INSTANCE CR HID MAOS ROSAS 30g</t>
+        </is>
+      </c>
+      <c r="C5123" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5124">
+      <c r="A5124" t="inlineStr">
+        <is>
+          <t>94220</t>
+        </is>
+      </c>
+      <c r="B5124" t="inlineStr">
+        <is>
+          <t>EUDORA MAKE CORRETIVO LÍQUIDO SKIN PERFECTION COR 120N 4ml</t>
+        </is>
+      </c>
+      <c r="C5124" t="inlineStr">
         <is>
           <t>Eudora</t>
         </is>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5124"/>
+  <dimension ref="A1:C5137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87524,6 +87524,227 @@
         </is>
       </c>
       <c r="C5124" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5125">
+      <c r="A5125" t="inlineStr">
+        <is>
+          <t>96125</t>
+        </is>
+      </c>
+      <c r="B5125" t="inlineStr">
+        <is>
+          <t>PRESENTE FLORATTA ROSE SUCRÉE</t>
+        </is>
+      </c>
+      <c r="C5125" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5126">
+      <c r="A5126" t="inlineStr">
+        <is>
+          <t>88135</t>
+        </is>
+      </c>
+      <c r="B5126" t="inlineStr">
+        <is>
+          <t>FLORATTA ROSE SUCRÉE EAU DE PARFUM, 75 ml</t>
+        </is>
+      </c>
+      <c r="C5126" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5127">
+      <c r="A5127" t="inlineStr">
+        <is>
+          <t>88467</t>
+        </is>
+      </c>
+      <c r="B5127" t="inlineStr">
+        <is>
+          <t>FLORATTA CR HID DES CPO ROSE SUCREE 200g</t>
+        </is>
+      </c>
+      <c r="C5127" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5128">
+      <c r="A5128" t="inlineStr">
+        <is>
+          <t>85018</t>
+        </is>
+      </c>
+      <c r="B5128" t="inlineStr">
+        <is>
+          <t>EUD MAKE BASE LIQUIDA SKIN PERFECTION 235N</t>
+        </is>
+      </c>
+      <c r="C5128" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5129">
+      <c r="A5129" t="inlineStr">
+        <is>
+          <t>85021</t>
+        </is>
+      </c>
+      <c r="B5129" t="inlineStr">
+        <is>
+          <t>EUD MAKE BASE LIQUIDA SKIN PERFECTION 250Q</t>
+        </is>
+      </c>
+      <c r="C5129" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5130">
+      <c r="A5130" t="inlineStr">
+        <is>
+          <t>94572</t>
+        </is>
+      </c>
+      <c r="B5130" t="inlineStr">
+        <is>
+          <t>DR BOTICA COL POC/CRIATIV V2 120ml</t>
+        </is>
+      </c>
+      <c r="C5130" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5131">
+      <c r="A5131" t="inlineStr">
+        <is>
+          <t>85012</t>
+        </is>
+      </c>
+      <c r="B5131" t="inlineStr">
+        <is>
+          <t>EUD MAKE BASE LIQUIDA SKIN PERFECTION 170Q</t>
+        </is>
+      </c>
+      <c r="C5131" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5132">
+      <c r="A5132" t="inlineStr">
+        <is>
+          <t>85017</t>
+        </is>
+      </c>
+      <c r="B5132" t="inlineStr">
+        <is>
+          <t>EUD MAKE BASE LIQUIDA SKIN PERFECTION 225N</t>
+        </is>
+      </c>
+      <c r="C5132" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5133">
+      <c r="A5133" t="inlineStr">
+        <is>
+          <t>85022</t>
+        </is>
+      </c>
+      <c r="B5133" t="inlineStr">
+        <is>
+          <t>EUD MAKE BASE LIQUIDA SKIN PERFECTION 260N</t>
+        </is>
+      </c>
+      <c r="C5133" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5134">
+      <c r="A5134" t="inlineStr">
+        <is>
+          <t>97241</t>
+        </is>
+      </c>
+      <c r="B5134" t="inlineStr">
+        <is>
+          <t>KIT PAPEL SEDA BOTI MAES 2026 C/20 VD</t>
+        </is>
+      </c>
+      <c r="C5134" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5135">
+      <c r="A5135" t="inlineStr">
+        <is>
+          <t>94228</t>
+        </is>
+      </c>
+      <c r="B5135" t="inlineStr">
+        <is>
+          <t>EUDORA MAKE CORRETIVO LÍQUIDO SKIN PERFECTION COR 250N 4ml</t>
+        </is>
+      </c>
+      <c r="C5135" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5136">
+      <c r="A5136" t="inlineStr">
+        <is>
+          <t>88620</t>
+        </is>
+      </c>
+      <c r="B5136" t="inlineStr">
+        <is>
+          <t>QDB BAT HID DOURALEXO RPCK V2 3,8g</t>
+        </is>
+      </c>
+      <c r="C5136" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="5137">
+      <c r="A5137" t="inlineStr">
+        <is>
+          <t>85317</t>
+        </is>
+      </c>
+      <c r="B5137" t="inlineStr">
+        <is>
+          <t>INSTANCE CR HID MAOS KARITE RPCK 30g</t>
+        </is>
+      </c>
+      <c r="C5137" t="inlineStr">
         <is>
           <t>Eudora</t>
         </is>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5137"/>
+  <dimension ref="A1:C5139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87745,6 +87745,40 @@
         </is>
       </c>
       <c r="C5137" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5138">
+      <c r="A5138" t="inlineStr">
+        <is>
+          <t>94222</t>
+        </is>
+      </c>
+      <c r="B5138" t="inlineStr">
+        <is>
+          <t>EUDORA MAKE CORRETIVO LÍQUIDO SKIN PERFECTION COR 190Q 4ml</t>
+        </is>
+      </c>
+      <c r="C5138" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5139">
+      <c r="A5139" t="inlineStr">
+        <is>
+          <t>94229</t>
+        </is>
+      </c>
+      <c r="B5139" t="inlineStr">
+        <is>
+          <t>EUDORA MAKE CORRETIVO LÍQUIDO SKIN PERFECTION COR 260Q 4ml</t>
+        </is>
+      </c>
+      <c r="C5139" t="inlineStr">
         <is>
           <t>Eudora</t>
         </is>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5139"/>
+  <dimension ref="A1:C5146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87781,6 +87781,125 @@
       <c r="C5139" t="inlineStr">
         <is>
           <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5140">
+      <c r="A5140" t="inlineStr">
+        <is>
+          <t>90321</t>
+        </is>
+      </c>
+      <c r="B5140" t="inlineStr">
+        <is>
+          <t>ZAAD EDP MONDO V5 95ml</t>
+        </is>
+      </c>
+      <c r="C5140" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5141">
+      <c r="A5141" t="inlineStr">
+        <is>
+          <t>96052</t>
+        </is>
+      </c>
+      <c r="B5141" t="inlineStr">
+        <is>
+          <t>COMBO NIINA MOUSSE DE LIMPEZA + PRO COLÁGENO</t>
+        </is>
+      </c>
+      <c r="C5141" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5142">
+      <c r="A5142" t="inlineStr">
+        <is>
+          <t>85016</t>
+        </is>
+      </c>
+      <c r="B5142" t="inlineStr">
+        <is>
+          <t>EUD MAKE BASE LIQUIDA SKIN PERFECTION 215N</t>
+        </is>
+      </c>
+      <c r="C5142" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5143">
+      <c r="A5143" t="inlineStr">
+        <is>
+          <t>85008</t>
+        </is>
+      </c>
+      <c r="B5143" t="inlineStr">
+        <is>
+          <t>EUD MAKE BASE LIQUIDA SKIN PERFECTION 100F</t>
+        </is>
+      </c>
+      <c r="C5143" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5144">
+      <c r="A5144" t="inlineStr">
+        <is>
+          <t>54325</t>
+        </is>
+      </c>
+      <c r="B5144" t="inlineStr">
+        <is>
+          <t>UOMINI BOLSA RETANG MARROM PU NAT/23</t>
+        </is>
+      </c>
+      <c r="C5144" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5145">
+      <c r="A5145" t="inlineStr">
+        <is>
+          <t>49215</t>
+        </is>
+      </c>
+      <c r="B5145" t="inlineStr">
+        <is>
+          <t>Nécessaire Cuide-se Bem Pessegura</t>
+        </is>
+      </c>
+      <c r="C5145" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5146">
+      <c r="A5146" t="inlineStr">
+        <is>
+          <t>49242</t>
+        </is>
+      </c>
+      <c r="B5146" t="inlineStr">
+        <is>
+          <t>COFFEE DES ANTIT AER WOM/SEDUC V5 75g</t>
+        </is>
+      </c>
+      <c r="C5146" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
         </is>
       </c>
     </row>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5146"/>
+  <dimension ref="A1:C5150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87898,6 +87898,74 @@
         </is>
       </c>
       <c r="C5146" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5147">
+      <c r="A5147" t="inlineStr">
+        <is>
+          <t>97816</t>
+        </is>
+      </c>
+      <c r="B5147" t="inlineStr">
+        <is>
+          <t>Combo Nativa Spa Rosas Secretas (12 itens)</t>
+        </is>
+      </c>
+      <c r="C5147" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5148">
+      <c r="A5148" t="inlineStr">
+        <is>
+          <t>95689</t>
+        </is>
+      </c>
+      <c r="B5148" t="inlineStr">
+        <is>
+          <t>[EUD - VD] MÃES 2026 - COMBO NIINA SECRETS COM ATÉ 25% DE DESCONTO</t>
+        </is>
+      </c>
+      <c r="C5148" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5149">
+      <c r="A5149" t="inlineStr">
+        <is>
+          <t>87477</t>
+        </is>
+      </c>
+      <c r="B5149" t="inlineStr">
+        <is>
+          <t>QDB BAT LIQ CR DOS SONHOS VERMEL V2 4ml</t>
+        </is>
+      </c>
+      <c r="C5149" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="5150">
+      <c r="A5150" t="inlineStr">
+        <is>
+          <t>97244</t>
+        </is>
+      </c>
+      <c r="B5150" t="inlineStr">
+        <is>
+          <t>KIT ADESIVOS BOTI MAES 2026 C/20 VD</t>
+        </is>
+      </c>
+      <c r="C5150" t="inlineStr">
         <is>
           <t>oBoticário</t>
         </is>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5150"/>
+  <dimension ref="A1:C5152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87968,6 +87968,40 @@
       <c r="C5150" t="inlineStr">
         <is>
           <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5151">
+      <c r="A5151" t="inlineStr">
+        <is>
+          <t>97813</t>
+        </is>
+      </c>
+      <c r="B5151" t="inlineStr">
+        <is>
+          <t>Combo Boti Baby (5 itens)</t>
+        </is>
+      </c>
+      <c r="C5151" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5152">
+      <c r="A5152" t="inlineStr">
+        <is>
+          <t>47160</t>
+        </is>
+      </c>
+      <c r="B5152" t="inlineStr">
+        <is>
+          <t>OUI CAIXA P 2021</t>
+        </is>
+      </c>
+      <c r="C5152" t="inlineStr">
+        <is>
+          <t>O.U.I</t>
         </is>
       </c>
     </row>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5152"/>
+  <dimension ref="A1:C5158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88002,6 +88002,108 @@
       <c r="C5152" t="inlineStr">
         <is>
           <t>O.U.I</t>
+        </is>
+      </c>
+    </row>
+    <row r="5153">
+      <c r="A5153" t="inlineStr">
+        <is>
+          <t>88471</t>
+        </is>
+      </c>
+      <c r="B5153" t="inlineStr">
+        <is>
+          <t>BOTIK GEL CREM REDUT RUG RET/PURO V2 30g</t>
+        </is>
+      </c>
+      <c r="C5153" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5154">
+      <c r="A5154" t="inlineStr">
+        <is>
+          <t>85015</t>
+        </is>
+      </c>
+      <c r="B5154" t="inlineStr">
+        <is>
+          <t>EUD MAKE BASE LIQUIDA SKIN PERFECTION 210Q</t>
+        </is>
+      </c>
+      <c r="C5154" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5155">
+      <c r="A5155" t="inlineStr">
+        <is>
+          <t>85024</t>
+        </is>
+      </c>
+      <c r="B5155" t="inlineStr">
+        <is>
+          <t>EUD MAKE BASE LIQUIDA SKIN PERFECTION 275N</t>
+        </is>
+      </c>
+      <c r="C5155" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5156">
+      <c r="A5156" t="inlineStr">
+        <is>
+          <t>88100</t>
+        </is>
+      </c>
+      <c r="B5156" t="inlineStr">
+        <is>
+          <t>QDB LIP TINT AVELA ROSADO 4ml</t>
+        </is>
+      </c>
+      <c r="C5156" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="5157">
+      <c r="A5157" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="B5157" t="inlineStr">
+        <is>
+          <t>QDB BAT LIQ SUPERMATE NUDELILI 4ml</t>
+        </is>
+      </c>
+      <c r="C5157" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="5158">
+      <c r="A5158" t="inlineStr">
+        <is>
+          <t>58566</t>
+        </is>
+      </c>
+      <c r="B5158" t="inlineStr">
+        <is>
+          <t>MAKE B CORRET LIQ FAC EFFECT 10 V2 5,7ml</t>
+        </is>
+      </c>
+      <c r="C5158" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
         </is>
       </c>
     </row>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5158"/>
+  <dimension ref="A1:C5180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88102,6 +88102,380 @@
         </is>
       </c>
       <c r="C5158" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5159">
+      <c r="A5159" t="inlineStr">
+        <is>
+          <t>96042</t>
+        </is>
+      </c>
+      <c r="B5159" t="inlineStr">
+        <is>
+          <t>Combo Nativa Spa Uva Merlot (2 Itens)</t>
+        </is>
+      </c>
+      <c r="C5159" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5160">
+      <c r="A5160" t="inlineStr">
+        <is>
+          <t>90219</t>
+        </is>
+      </c>
+      <c r="B5160" t="inlineStr">
+        <is>
+          <t>CBEM DES COL BDY SPLSH DEL/CARAM 200ml</t>
+        </is>
+      </c>
+      <c r="C5160" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5161">
+      <c r="A5161" t="inlineStr">
+        <is>
+          <t>89663</t>
+        </is>
+      </c>
+      <c r="B5161" t="inlineStr">
+        <is>
+          <t>CBEM SAB BARRA DELEITE ESPEC 2x90g</t>
+        </is>
+      </c>
+      <c r="C5161" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5162">
+      <c r="A5162" t="inlineStr">
+        <is>
+          <t>89658</t>
+        </is>
+      </c>
+      <c r="B5162" t="inlineStr">
+        <is>
+          <t>CBEM MANTG DES HID CPO DELEITE 200g</t>
+        </is>
+      </c>
+      <c r="C5162" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5163">
+      <c r="A5163" t="inlineStr">
+        <is>
+          <t>96214</t>
+        </is>
+      </c>
+      <c r="B5163" t="inlineStr">
+        <is>
+          <t>PRESENTE NATIVA SPA LILAC</t>
+        </is>
+      </c>
+      <c r="C5163" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5164">
+      <c r="A5164" t="inlineStr">
+        <is>
+          <t>89660</t>
+        </is>
+      </c>
+      <c r="B5164" t="inlineStr">
+        <is>
+          <t>CBEM MANTG DES HID CPO DEL/CARAMEL 200g</t>
+        </is>
+      </c>
+      <c r="C5164" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5165">
+      <c r="A5165" t="inlineStr">
+        <is>
+          <t>96467</t>
+        </is>
+      </c>
+      <c r="B5165" t="inlineStr">
+        <is>
+          <t>PRESENTE CUIDE-SE BEM CREMOSÍSSIMO</t>
+        </is>
+      </c>
+      <c r="C5165" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5166">
+      <c r="A5166" t="inlineStr">
+        <is>
+          <t>89662</t>
+        </is>
+      </c>
+      <c r="B5166" t="inlineStr">
+        <is>
+          <t>CBEM LOC DES HID CPO DEL/CARAMEL 400ml</t>
+        </is>
+      </c>
+      <c r="C5166" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5167">
+      <c r="A5167" t="inlineStr">
+        <is>
+          <t>97919</t>
+        </is>
+      </c>
+      <c r="B5167" t="inlineStr">
+        <is>
+          <t>Combo Sophie 1 (3 Itens)</t>
+        </is>
+      </c>
+      <c r="C5167" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5168">
+      <c r="A5168" t="inlineStr">
+        <is>
+          <t>97851</t>
+        </is>
+      </c>
+      <c r="B5168" t="inlineStr">
+        <is>
+          <t>Combo Siage Liso Intenso (4 itens)</t>
+        </is>
+      </c>
+      <c r="C5168" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5169">
+      <c r="A5169" t="inlineStr">
+        <is>
+          <t>90998</t>
+        </is>
+      </c>
+      <c r="B5169" t="inlineStr">
+        <is>
+          <t>CBEM SAB LIQ CPO DEL/CARAMEL 150ml</t>
+        </is>
+      </c>
+      <c r="C5169" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5170">
+      <c r="A5170" t="inlineStr">
+        <is>
+          <t>89484</t>
+        </is>
+      </c>
+      <c r="B5170" t="inlineStr">
+        <is>
+          <t>NSPA TRIO SAB BARR BES SEL COLL 3x100g</t>
+        </is>
+      </c>
+      <c r="C5170" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5171">
+      <c r="A5171" t="inlineStr">
+        <is>
+          <t>95821</t>
+        </is>
+      </c>
+      <c r="B5171" t="inlineStr">
+        <is>
+          <t>PRESENTE CUIDE-SE BEM AMORUDA</t>
+        </is>
+      </c>
+      <c r="C5171" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5172">
+      <c r="A5172" t="inlineStr">
+        <is>
+          <t>96097</t>
+        </is>
+      </c>
+      <c r="B5172" t="inlineStr">
+        <is>
+          <t>PRESENTE FLORATTA ROSE</t>
+        </is>
+      </c>
+      <c r="C5172" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5173">
+      <c r="A5173" t="inlineStr">
+        <is>
+          <t>97849</t>
+        </is>
+      </c>
+      <c r="B5173" t="inlineStr">
+        <is>
+          <t>Combo Malbec (4 Itens)</t>
+        </is>
+      </c>
+      <c r="C5173" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5174">
+      <c r="A5174" t="inlineStr">
+        <is>
+          <t>96489</t>
+        </is>
+      </c>
+      <c r="B5174" t="inlineStr">
+        <is>
+          <t>PRESENTE L'EAU DE LILY</t>
+        </is>
+      </c>
+      <c r="C5174" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5175">
+      <c r="A5175" t="inlineStr">
+        <is>
+          <t>96124</t>
+        </is>
+      </c>
+      <c r="B5175" t="inlineStr">
+        <is>
+          <t>PRESENTE COFFEE</t>
+        </is>
+      </c>
+      <c r="C5175" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5176">
+      <c r="A5176" t="inlineStr">
+        <is>
+          <t>95819</t>
+        </is>
+      </c>
+      <c r="B5176" t="inlineStr">
+        <is>
+          <t>PRESENTE EGEO ILLUSION</t>
+        </is>
+      </c>
+      <c r="C5176" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5177">
+      <c r="A5177" t="inlineStr">
+        <is>
+          <t>95804</t>
+        </is>
+      </c>
+      <c r="B5177" t="inlineStr">
+        <is>
+          <t>PRESENTE CUIDE-SE BEM CEREJA LIVRE</t>
+        </is>
+      </c>
+      <c r="C5177" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5178">
+      <c r="A5178" t="inlineStr">
+        <is>
+          <t>88821</t>
+        </is>
+      </c>
+      <c r="B5178" t="inlineStr">
+        <is>
+          <t>CASA 214 DIFUSOR VARETA FIGO/MAGNF 250ml</t>
+        </is>
+      </c>
+      <c r="C5178" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5179">
+      <c r="A5179" t="inlineStr">
+        <is>
+          <t>94966</t>
+        </is>
+      </c>
+      <c r="B5179" t="inlineStr">
+        <is>
+          <t>FLORATTA CR DES HID CPO RED/PASS 200g</t>
+        </is>
+      </c>
+      <c r="C5179" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5180">
+      <c r="A5180" t="inlineStr">
+        <is>
+          <t>90140</t>
+        </is>
+      </c>
+      <c r="B5180" t="inlineStr">
+        <is>
+          <t>REF CASA 214 SAB LIQ MAO FIG/MAGNF 250ml</t>
+        </is>
+      </c>
+      <c r="C5180" t="inlineStr">
         <is>
           <t>oBoticário</t>
         </is>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5180"/>
+  <dimension ref="A1:C5194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88476,6 +88476,244 @@
         </is>
       </c>
       <c r="C5180" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5181">
+      <c r="A5181" t="inlineStr">
+        <is>
+          <t>95820</t>
+        </is>
+      </c>
+      <c r="B5181" t="inlineStr">
+        <is>
+          <t>COMB LIZ AURA MAES/26</t>
+        </is>
+      </c>
+      <c r="C5181" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5182">
+      <c r="A5182" t="inlineStr">
+        <is>
+          <t>96075</t>
+        </is>
+      </c>
+      <c r="B5182" t="inlineStr">
+        <is>
+          <t>PRESENTE GLAMOUR</t>
+        </is>
+      </c>
+      <c r="C5182" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5183">
+      <c r="A5183" t="inlineStr">
+        <is>
+          <t>97814</t>
+        </is>
+      </c>
+      <c r="B5183" t="inlineStr">
+        <is>
+          <t>Combo OUI Mon Amie 037 (3 itens)</t>
+        </is>
+      </c>
+      <c r="C5183" t="inlineStr">
+        <is>
+          <t>O.U.I</t>
+        </is>
+      </c>
+    </row>
+    <row r="5184">
+      <c r="A5184" t="inlineStr">
+        <is>
+          <t>95822</t>
+        </is>
+      </c>
+      <c r="B5184" t="inlineStr">
+        <is>
+          <t>PRESENTE HER CODE TOUCH</t>
+        </is>
+      </c>
+      <c r="C5184" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5185">
+      <c r="A5185" t="inlineStr">
+        <is>
+          <t>96080</t>
+        </is>
+      </c>
+      <c r="B5185" t="inlineStr">
+        <is>
+          <t>COMB BOTICA 214 AFRIC/SUNR MAES/26</t>
+        </is>
+      </c>
+      <c r="C5185" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5186">
+      <c r="A5186" t="inlineStr">
+        <is>
+          <t>96044</t>
+        </is>
+      </c>
+      <c r="B5186" t="inlineStr">
+        <is>
+          <t>PRESENTE FLORATTA BLUE</t>
+        </is>
+      </c>
+      <c r="C5186" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5187">
+      <c r="A5187" t="inlineStr">
+        <is>
+          <t>95805</t>
+        </is>
+      </c>
+      <c r="B5187" t="inlineStr">
+        <is>
+          <t>PRESENTE NATIVA SPA ORQUÍDEA LUMIÈRE</t>
+        </is>
+      </c>
+      <c r="C5187" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5188">
+      <c r="A5188" t="inlineStr">
+        <is>
+          <t>96663</t>
+        </is>
+      </c>
+      <c r="B5188" t="inlineStr">
+        <is>
+          <t>PRESENTE NATIVA SPA ORQUÍDEA NOIRE</t>
+        </is>
+      </c>
+      <c r="C5188" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5189">
+      <c r="A5189" t="inlineStr">
+        <is>
+          <t>96217</t>
+        </is>
+      </c>
+      <c r="B5189" t="inlineStr">
+        <is>
+          <t>PRESENTE EGEO RED E MAKE B</t>
+        </is>
+      </c>
+      <c r="C5189" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5190">
+      <c r="A5190" t="inlineStr">
+        <is>
+          <t>95796</t>
+        </is>
+      </c>
+      <c r="B5190" t="inlineStr">
+        <is>
+          <t>PRESENTE CUIDE-SE BEM BOA NOITE</t>
+        </is>
+      </c>
+      <c r="C5190" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5191">
+      <c r="A5191" t="inlineStr">
+        <is>
+          <t>96906</t>
+        </is>
+      </c>
+      <c r="B5191" t="inlineStr">
+        <is>
+          <t>PRESENTE FLORATTA BLUE CUIDADOS</t>
+        </is>
+      </c>
+      <c r="C5191" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5192">
+      <c r="A5192" t="inlineStr">
+        <is>
+          <t>87132</t>
+        </is>
+      </c>
+      <c r="B5192" t="inlineStr">
+        <is>
+          <t>REF INSTANC LOC DES H CPO KAR RPCK 350ml</t>
+        </is>
+      </c>
+      <c r="C5192" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5193">
+      <c r="A5193" t="inlineStr">
+        <is>
+          <t>88138</t>
+        </is>
+      </c>
+      <c r="B5193" t="inlineStr">
+        <is>
+          <t>DEM FLORATTA EDP ROSE SUCREE 4ml</t>
+        </is>
+      </c>
+      <c r="C5193" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5194">
+      <c r="A5194" t="inlineStr">
+        <is>
+          <t>96651</t>
+        </is>
+      </c>
+      <c r="B5194" t="inlineStr">
+        <is>
+          <t>CATALOGO BOTICARIO NNE CICLO 07/26</t>
+        </is>
+      </c>
+      <c r="C5194" t="inlineStr">
         <is>
           <t>oBoticário</t>
         </is>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5194"/>
+  <dimension ref="A1:C5201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88714,6 +88714,125 @@
         </is>
       </c>
       <c r="C5194" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5195">
+      <c r="A5195" t="inlineStr">
+        <is>
+          <t>55295</t>
+        </is>
+      </c>
+      <c r="B5195" t="inlineStr">
+        <is>
+          <t>EUDORA ROYAL DESODORANTE COLONIA FEMININO 100ml</t>
+        </is>
+      </c>
+      <c r="C5195" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5196">
+      <c r="A5196" t="inlineStr">
+        <is>
+          <t>55296</t>
+        </is>
+      </c>
+      <c r="B5196" t="inlineStr">
+        <is>
+          <t>EUDORA ROYAL DESODORANTE COLONIA MASCULINO 100ml</t>
+        </is>
+      </c>
+      <c r="C5196" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5197">
+      <c r="A5197" t="inlineStr">
+        <is>
+          <t>49244</t>
+        </is>
+      </c>
+      <c r="B5197" t="inlineStr">
+        <is>
+          <t>COFFEE D/COL MAN ORIENT/AMB V4 100ml</t>
+        </is>
+      </c>
+      <c r="C5197" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5198">
+      <c r="A5198" t="inlineStr">
+        <is>
+          <t>97920</t>
+        </is>
+      </c>
+      <c r="B5198" t="inlineStr">
+        <is>
+          <t>Combo Sophie 2 (3 Itens)</t>
+        </is>
+      </c>
+      <c r="C5198" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5199">
+      <c r="A5199" t="inlineStr">
+        <is>
+          <t>96491</t>
+        </is>
+      </c>
+      <c r="B5199" t="inlineStr">
+        <is>
+          <t>COMB ROYAL MASC AMOR/26</t>
+        </is>
+      </c>
+      <c r="C5199" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5200">
+      <c r="A5200" t="inlineStr">
+        <is>
+          <t>96490</t>
+        </is>
+      </c>
+      <c r="B5200" t="inlineStr">
+        <is>
+          <t>COMB ROYAL FEM AMOR/26</t>
+        </is>
+      </c>
+      <c r="C5200" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5201">
+      <c r="A5201" t="inlineStr">
+        <is>
+          <t>88823</t>
+        </is>
+      </c>
+      <c r="B5201" t="inlineStr">
+        <is>
+          <t>CASA 214 AROMAT/AMB SPR FIGO/MAGNF 250ml</t>
+        </is>
+      </c>
+      <c r="C5201" t="inlineStr">
         <is>
           <t>oBoticário</t>
         </is>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5201"/>
+  <dimension ref="A1:C5204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88835,6 +88835,57 @@
       <c r="C5201" t="inlineStr">
         <is>
           <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5202">
+      <c r="A5202" t="inlineStr">
+        <is>
+          <t>94371</t>
+        </is>
+      </c>
+      <c r="B5202" t="inlineStr">
+        <is>
+          <t>SACOLA M EUDORA UNIT MAES 2026</t>
+        </is>
+      </c>
+      <c r="C5202" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5203">
+      <c r="A5203" t="inlineStr">
+        <is>
+          <t>94997</t>
+        </is>
+      </c>
+      <c r="B5203" t="inlineStr">
+        <is>
+          <t>DEM EUD ROYAL DES COL FEM 4ml</t>
+        </is>
+      </c>
+      <c r="C5203" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5204">
+      <c r="A5204" t="inlineStr">
+        <is>
+          <t>94998</t>
+        </is>
+      </c>
+      <c r="B5204" t="inlineStr">
+        <is>
+          <t>DEM EUD ROYAL DES COL MASC 4ml</t>
+        </is>
+      </c>
+      <c r="C5204" t="inlineStr">
+        <is>
+          <t>Eudora</t>
         </is>
       </c>
     </row>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5204"/>
+  <dimension ref="A1:C5207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88886,6 +88886,57 @@
       <c r="C5204" t="inlineStr">
         <is>
           <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5205">
+      <c r="A5205" t="inlineStr">
+        <is>
+          <t>96099</t>
+        </is>
+      </c>
+      <c r="B5205" t="inlineStr">
+        <is>
+          <t>COMB LILY LUMIER MAES/26</t>
+        </is>
+      </c>
+      <c r="C5205" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5206">
+      <c r="A5206" t="inlineStr">
+        <is>
+          <t>88695</t>
+        </is>
+      </c>
+      <c r="B5206" t="inlineStr">
+        <is>
+          <t>CBEM LOC DES HID CP R/ALG N/FORM 200ml</t>
+        </is>
+      </c>
+      <c r="C5206" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5207">
+      <c r="A5207" t="inlineStr">
+        <is>
+          <t>94673</t>
+        </is>
+      </c>
+      <c r="B5207" t="inlineStr">
+        <is>
+          <t>CBEM GEL LIMP FAC FEIR TANGERINA V2 150g</t>
+        </is>
+      </c>
+      <c r="C5207" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
         </is>
       </c>
     </row>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5207"/>
+  <dimension ref="A1:C5209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88935,6 +88935,40 @@
         </is>
       </c>
       <c r="C5207" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5208">
+      <c r="A5208" t="inlineStr">
+        <is>
+          <t>96098</t>
+        </is>
+      </c>
+      <c r="B5208" t="inlineStr">
+        <is>
+          <t>COMB ELYSEE BLANC MAES/26</t>
+        </is>
+      </c>
+      <c r="C5208" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5209">
+      <c r="A5209" t="inlineStr">
+        <is>
+          <t>97921</t>
+        </is>
+      </c>
+      <c r="B5209" t="inlineStr">
+        <is>
+          <t>Combo Sophie (6 Itens)</t>
+        </is>
+      </c>
+      <c r="C5209" t="inlineStr">
         <is>
           <t>oBoticário</t>
         </is>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5209"/>
+  <dimension ref="A1:C5216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88969,6 +88969,125 @@
         </is>
       </c>
       <c r="C5209" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5210">
+      <c r="A5210" t="inlineStr">
+        <is>
+          <t>49247</t>
+        </is>
+      </c>
+      <c r="B5210" t="inlineStr">
+        <is>
+          <t>COFFEE D/COL SEDUC MAN OR/AMAD V5 100ml</t>
+        </is>
+      </c>
+      <c r="C5210" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5211">
+      <c r="A5211" t="inlineStr">
+        <is>
+          <t>88822</t>
+        </is>
+      </c>
+      <c r="B5211" t="inlineStr">
+        <is>
+          <t>CASA 214 VELA PERF FIGO/MAGNF 170g</t>
+        </is>
+      </c>
+      <c r="C5211" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5212">
+      <c r="A5212" t="inlineStr">
+        <is>
+          <t>88633</t>
+        </is>
+      </c>
+      <c r="B5212" t="inlineStr">
+        <is>
+          <t>OUI LOC DES HID CPO PARADIS/RGE V2 400ml</t>
+        </is>
+      </c>
+      <c r="C5212" t="inlineStr">
+        <is>
+          <t>O.U.I</t>
+        </is>
+      </c>
+    </row>
+    <row r="5213">
+      <c r="A5213" t="inlineStr">
+        <is>
+          <t>85026</t>
+        </is>
+      </c>
+      <c r="B5213" t="inlineStr">
+        <is>
+          <t>EUD MAKE BASE LIQUIDA SKIN PERFECTION 288Q</t>
+        </is>
+      </c>
+      <c r="C5213" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5214">
+      <c r="A5214" t="inlineStr">
+        <is>
+          <t>87128</t>
+        </is>
+      </c>
+      <c r="B5214" t="inlineStr">
+        <is>
+          <t>INSTANCE LOC DES HID CPO FR/VERM 180ml</t>
+        </is>
+      </c>
+      <c r="C5214" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5215">
+      <c r="A5215" t="inlineStr">
+        <is>
+          <t>94510</t>
+        </is>
+      </c>
+      <c r="B5215" t="inlineStr">
+        <is>
+          <t>BOTIK BALM LAB HID AC/HIALUR V2 3,2g</t>
+        </is>
+      </c>
+      <c r="C5215" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5216">
+      <c r="A5216" t="inlineStr">
+        <is>
+          <t>96645</t>
+        </is>
+      </c>
+      <c r="B5216" t="inlineStr">
+        <is>
+          <t>CATALOGO BOTICARIO NNE CICLO 06/26</t>
+        </is>
+      </c>
+      <c r="C5216" t="inlineStr">
         <is>
           <t>oBoticário</t>
         </is>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5216"/>
+  <dimension ref="A1:C5226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89090,6 +89090,176 @@
       <c r="C5216" t="inlineStr">
         <is>
           <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5217">
+      <c r="A5217" t="inlineStr">
+        <is>
+          <t>96741</t>
+        </is>
+      </c>
+      <c r="B5217" t="inlineStr">
+        <is>
+          <t>COMB INSTANCE MORANGO/IRRES AMOR/26</t>
+        </is>
+      </c>
+      <c r="C5217" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5218">
+      <c r="A5218" t="inlineStr">
+        <is>
+          <t>56701</t>
+        </is>
+      </c>
+      <c r="B5218" t="inlineStr">
+        <is>
+          <t>COMBO SH+COND GLOW EXPERT DE R$ 86,98 POR R$ 73,99</t>
+        </is>
+      </c>
+      <c r="C5218" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5219">
+      <c r="A5219" t="inlineStr">
+        <is>
+          <t>95912</t>
+        </is>
+      </c>
+      <c r="B5219" t="inlineStr">
+        <is>
+          <t>COMB INSTANCE AMEIXA/PRALINE AMOR/26</t>
+        </is>
+      </c>
+      <c r="C5219" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5220">
+      <c r="A5220" t="inlineStr">
+        <is>
+          <t>96752</t>
+        </is>
+      </c>
+      <c r="B5220" t="inlineStr">
+        <is>
+          <t>COMB MAGNIFIC VIOLET DAHLIA AMOR/26</t>
+        </is>
+      </c>
+      <c r="C5220" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5221">
+      <c r="A5221" t="inlineStr">
+        <is>
+          <t>89451</t>
+        </is>
+      </c>
+      <c r="B5221" t="inlineStr">
+        <is>
+          <t>INSTANCE LOCAO HIDRATANTE DESODORANTE CORPORAL MORANGO IRRESISTIVEL 400ml</t>
+        </is>
+      </c>
+      <c r="C5221" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5222">
+      <c r="A5222" t="inlineStr">
+        <is>
+          <t>58384</t>
+        </is>
+      </c>
+      <c r="B5222" t="inlineStr">
+        <is>
+          <t>COMBO SH+COND NUTRI ROSE POR R$ 74,99</t>
+        </is>
+      </c>
+      <c r="C5222" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5223">
+      <c r="A5223" t="inlineStr">
+        <is>
+          <t>95704</t>
+        </is>
+      </c>
+      <c r="B5223" t="inlineStr">
+        <is>
+          <t>COMB INSTANCE AMEIX/PRAL NAM/26</t>
+        </is>
+      </c>
+      <c r="C5223" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5224">
+      <c r="A5224" t="inlineStr">
+        <is>
+          <t>95705</t>
+        </is>
+      </c>
+      <c r="B5224" t="inlineStr">
+        <is>
+          <t>COMB INSTANCE AMEIX/PRAL NAM/26 02</t>
+        </is>
+      </c>
+      <c r="C5224" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5225">
+      <c r="A5225" t="inlineStr">
+        <is>
+          <t>89453</t>
+        </is>
+      </c>
+      <c r="B5225" t="inlineStr">
+        <is>
+          <t>INSTANCE SABONETE BARRA MORANGO IRRESISTIVEL 4x80g</t>
+        </is>
+      </c>
+      <c r="C5225" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5226">
+      <c r="A5226" t="inlineStr">
+        <is>
+          <t>49510</t>
+        </is>
+      </c>
+      <c r="B5226" t="inlineStr">
+        <is>
+          <t>DEM IMENSI DES COL 4ml V2 VDA</t>
+        </is>
+      </c>
+      <c r="C5226" t="inlineStr">
+        <is>
+          <t>Eudora</t>
         </is>
       </c>
     </row>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5226"/>
+  <dimension ref="A1:C5236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89260,6 +89260,176 @@
       <c r="C5226" t="inlineStr">
         <is>
           <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5227">
+      <c r="A5227" t="inlineStr">
+        <is>
+          <t>95697</t>
+        </is>
+      </c>
+      <c r="B5227" t="inlineStr">
+        <is>
+          <t>COMB PULSE BOOST NAM/26</t>
+        </is>
+      </c>
+      <c r="C5227" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5228">
+      <c r="A5228" t="inlineStr">
+        <is>
+          <t>95910</t>
+        </is>
+      </c>
+      <c r="B5228" t="inlineStr">
+        <is>
+          <t>COMB LYRA AMOR/26</t>
+        </is>
+      </c>
+      <c r="C5228" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5229">
+      <c r="A5229" t="inlineStr">
+        <is>
+          <t>95702</t>
+        </is>
+      </c>
+      <c r="B5229" t="inlineStr">
+        <is>
+          <t>COMB NIINA SCRT NEUTRALS NAM/26</t>
+        </is>
+      </c>
+      <c r="C5229" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5230">
+      <c r="A5230" t="inlineStr">
+        <is>
+          <t>48759</t>
+        </is>
+      </c>
+      <c r="B5230" t="inlineStr">
+        <is>
+          <t>MALBEC DES COL BLEU 50ml</t>
+        </is>
+      </c>
+      <c r="C5230" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5231">
+      <c r="A5231" t="inlineStr">
+        <is>
+          <t>95915</t>
+        </is>
+      </c>
+      <c r="B5231" t="inlineStr">
+        <is>
+          <t>COMB SIAGE HAIR PLASTIA AMOR/26</t>
+        </is>
+      </c>
+      <c r="C5231" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5232">
+      <c r="A5232" t="inlineStr">
+        <is>
+          <t>90479</t>
+        </is>
+      </c>
+      <c r="B5232" t="inlineStr">
+        <is>
+          <t>COMB SIAGE CAUTERIZ/FIOS</t>
+        </is>
+      </c>
+      <c r="C5232" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5233">
+      <c r="A5233" t="inlineStr">
+        <is>
+          <t>96751</t>
+        </is>
+      </c>
+      <c r="B5233" t="inlineStr">
+        <is>
+          <t>COMB EUD K/M DELICIOUS AMOR/26</t>
+        </is>
+      </c>
+      <c r="C5233" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5234">
+      <c r="A5234" t="inlineStr">
+        <is>
+          <t>95703</t>
+        </is>
+      </c>
+      <c r="B5234" t="inlineStr">
+        <is>
+          <t>COMB DIVA SUPREMA NAM/26</t>
+        </is>
+      </c>
+      <c r="C5234" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5235">
+      <c r="A5235" t="inlineStr">
+        <is>
+          <t>88820</t>
+        </is>
+      </c>
+      <c r="B5235" t="inlineStr">
+        <is>
+          <t>CASA 214 SAB LIQ MAOS FIGO/MAGNF 250ml</t>
+        </is>
+      </c>
+      <c r="C5235" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5236">
+      <c r="A5236" t="inlineStr">
+        <is>
+          <t>88102</t>
+        </is>
+      </c>
+      <c r="B5236" t="inlineStr">
+        <is>
+          <t>QDB LIP TINT ROSA MALVA 4ml</t>
+        </is>
+      </c>
+      <c r="C5236" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
         </is>
       </c>
     </row>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5236"/>
+  <dimension ref="A1:C5336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12397,7 +12397,7 @@
       </c>
       <c r="C704" s="1" t="inlineStr">
         <is>
-          <t>OBOTICÁRIO</t>
+          <t>Quem Disse Berenice</t>
         </is>
       </c>
     </row>
@@ -78850,7 +78850,7 @@
       </c>
       <c r="C4613" s="1" t="inlineStr">
         <is>
-          <t>OBOTICÁRIO</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
@@ -79190,7 +79190,7 @@
       </c>
       <c r="C4633" s="1" t="inlineStr">
         <is>
-          <t>OBOTICÁRIO</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
@@ -79241,7 +79241,7 @@
       </c>
       <c r="C4636" s="1" t="inlineStr">
         <is>
-          <t>OBOTICÁRIO</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
@@ -79428,7 +79428,7 @@
       </c>
       <c r="C4647" s="1" t="inlineStr">
         <is>
-          <t>OBOTICÁRIO</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
@@ -79462,7 +79462,7 @@
       </c>
       <c r="C4649" s="1" t="inlineStr">
         <is>
-          <t>OBOTICÁRIO</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
@@ -79564,7 +79564,7 @@
       </c>
       <c r="C4655" s="1" t="inlineStr">
         <is>
-          <t>OBOTICÁRIO</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
@@ -79785,7 +79785,7 @@
       </c>
       <c r="C4668" s="1" t="inlineStr">
         <is>
-          <t>OBOTICÁRIO</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
@@ -79887,7 +79887,7 @@
       </c>
       <c r="C4674" s="1" t="inlineStr">
         <is>
-          <t>OBOTICÁRIO</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
@@ -79904,7 +79904,7 @@
       </c>
       <c r="C4675" s="1" t="inlineStr">
         <is>
-          <t>OBOTICÁRIO</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
@@ -81171,7 +81171,7 @@
       <c r="B4750" s="1" t="n"/>
       <c r="C4750" s="1" t="inlineStr">
         <is>
-          <t>EUD</t>
+          <t>oBoticário</t>
         </is>
       </c>
     </row>
@@ -82663,7 +82663,7 @@
       </c>
       <c r="C4838" s="1" t="inlineStr">
         <is>
-          <t>OBOTICÁRIO</t>
+          <t>O.U.I</t>
         </is>
       </c>
     </row>
@@ -82731,7 +82731,7 @@
       </c>
       <c r="C4842" s="1" t="inlineStr">
         <is>
-          <t>OBOTICÁRIO</t>
+          <t>Quem Disse Berenice</t>
         </is>
       </c>
     </row>
@@ -85349,7 +85349,7 @@
       </c>
       <c r="C4996" s="1" t="inlineStr">
         <is>
-          <t>oBoticário</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
@@ -85451,7 +85451,7 @@
       </c>
       <c r="C5002" s="1" t="inlineStr">
         <is>
-          <t>oBoticário</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
@@ -85638,7 +85638,7 @@
       </c>
       <c r="C5013" s="1" t="inlineStr">
         <is>
-          <t>oBoticário</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
@@ -85774,7 +85774,7 @@
       </c>
       <c r="C5021" s="1" t="inlineStr">
         <is>
-          <t>oBoticário</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
@@ -85944,7 +85944,7 @@
       </c>
       <c r="C5031" s="1" t="inlineStr">
         <is>
-          <t>oBoticário</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
@@ -86194,7 +86194,7 @@
       </c>
       <c r="B5046" t="inlineStr">
         <is>
-          <t>[EUD - VD] MÃES 2026 - COMBO INSTANCE COM ATÉ 37% DE DESCONTO</t>
+          <t>COMB INSTANCE BAUNILHA INTENSA MAES/26</t>
         </is>
       </c>
       <c r="C5046" t="inlineStr">
@@ -86216,7 +86216,7 @@
       </c>
       <c r="C5047" t="inlineStr">
         <is>
-          <t>oBoticário</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
@@ -86432,7 +86432,7 @@
       </c>
       <c r="B5060" t="inlineStr">
         <is>
-          <t>[EUD - VD] LANÇAMENTO MÃES 2026 - COMBO BAUNILHA INTENSA COM ATÉ 21% DE DESCONTO</t>
+          <t>COMB INSTANCE BAUNILHA INTENSA MAES/26</t>
         </is>
       </c>
       <c r="C5060" t="inlineStr">
@@ -86500,7 +86500,7 @@
       </c>
       <c r="B5064" t="inlineStr">
         <is>
-          <t>COMBO MON AMIE</t>
+          <t>COMB OUI MON AMIE 037 MAES/26</t>
         </is>
       </c>
       <c r="C5064" t="inlineStr">
@@ -86828,7 +86828,7 @@
       </c>
       <c r="C5083" t="inlineStr">
         <is>
-          <t>oBoticário</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
@@ -89430,6 +89430,1706 @@
       <c r="C5236" t="inlineStr">
         <is>
           <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="5237">
+      <c r="A5237" t="inlineStr">
+        <is>
+          <t>87842</t>
+        </is>
+      </c>
+      <c r="B5237" t="inlineStr">
+        <is>
+          <t>THE BLEND EDP SAFFRON 100ml</t>
+        </is>
+      </c>
+      <c r="C5237" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5238">
+      <c r="A5238" t="inlineStr">
+        <is>
+          <t>86059</t>
+        </is>
+      </c>
+      <c r="B5238" t="inlineStr">
+        <is>
+          <t>SOPHIE SPLASH CORPO E CABELO SHIMMER CHAPÉU CINTILANTE, 110ml</t>
+        </is>
+      </c>
+      <c r="C5238" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5239">
+      <c r="A5239" t="inlineStr">
+        <is>
+          <t>86058</t>
+        </is>
+      </c>
+      <c r="B5239" t="inlineStr">
+        <is>
+          <t>SOPHIE SPLASH CORPO E CABELO SHIMMER BRILHO INTERGALÁCTICO, 110ml</t>
+        </is>
+      </c>
+      <c r="C5239" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5240">
+      <c r="A5240" t="inlineStr">
+        <is>
+          <t>86061</t>
+        </is>
+      </c>
+      <c r="B5240" t="inlineStr">
+        <is>
+          <t>SOPHIE SPLASH CORPO E CABELO SHIMMER AMIZADE ILUMINADA, 110ml</t>
+        </is>
+      </c>
+      <c r="C5240" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5241">
+      <c r="A5241" t="inlineStr">
+        <is>
+          <t>90819</t>
+        </is>
+      </c>
+      <c r="B5241" t="inlineStr">
+        <is>
+          <t>SACOLA PP BOTICARIO INST/25</t>
+        </is>
+      </c>
+      <c r="C5241" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5242">
+      <c r="A5242" t="inlineStr">
+        <is>
+          <t>94969</t>
+        </is>
+      </c>
+      <c r="B5242" t="inlineStr">
+        <is>
+          <t>ROYAL LOC DES HID CPO MASC 150ml</t>
+        </is>
+      </c>
+      <c r="C5242" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5243">
+      <c r="A5243" t="inlineStr">
+        <is>
+          <t>91000</t>
+        </is>
+      </c>
+      <c r="B5243" t="inlineStr">
+        <is>
+          <t>ROYAL LOC DES HID CPO 150ml</t>
+        </is>
+      </c>
+      <c r="C5243" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5244">
+      <c r="A5244" t="inlineStr">
+        <is>
+          <t>59525</t>
+        </is>
+      </c>
+      <c r="B5244" t="inlineStr">
+        <is>
+          <t>REF NSPA LOC DES HID CPO JASM/SAMB 350ml</t>
+        </is>
+      </c>
+      <c r="C5244" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5245">
+      <c r="A5245" t="inlineStr">
+        <is>
+          <t>89203</t>
+        </is>
+      </c>
+      <c r="B5245" t="inlineStr">
+        <is>
+          <t>QUEM DISSE, BERENICE? SWEET LAB MOCHI BLUR VERMELHO GOJI BERRY, 3,5g</t>
+        </is>
+      </c>
+      <c r="C5245" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="5246">
+      <c r="A5246" t="inlineStr">
+        <is>
+          <t>89205</t>
+        </is>
+      </c>
+      <c r="B5246" t="inlineStr">
+        <is>
+          <t>QUEM DISSE, BERENICE? SWEET LAB MOCHI BLUR ROXO AMORA FUJI, 3,5g</t>
+        </is>
+      </c>
+      <c r="C5246" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="5247">
+      <c r="A5247" t="inlineStr">
+        <is>
+          <t>89206</t>
+        </is>
+      </c>
+      <c r="B5247" t="inlineStr">
+        <is>
+          <t>QUEM DISSE, BERENICE? SWEET LAB MOCHI BLUR ROSA LICHIA SAKURA, 3,5g</t>
+        </is>
+      </c>
+      <c r="C5247" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="5248">
+      <c r="A5248" t="inlineStr">
+        <is>
+          <t>89204</t>
+        </is>
+      </c>
+      <c r="B5248" t="inlineStr">
+        <is>
+          <t>QUEM DISSE, BERENICE? SWEET LAB MOCHI BLUR MARROM CACAU MATCHA, 3,5g</t>
+        </is>
+      </c>
+      <c r="C5248" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="5249">
+      <c r="A5249" t="inlineStr">
+        <is>
+          <t>90534</t>
+        </is>
+      </c>
+      <c r="B5249" t="inlineStr">
+        <is>
+          <t>QDB GLOS DOS SONHOS ROSADEX V2 4ml</t>
+        </is>
+      </c>
+      <c r="C5249" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="5250">
+      <c r="A5250" t="inlineStr">
+        <is>
+          <t>86122</t>
+        </is>
+      </c>
+      <c r="B5250" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ POP 140N 30ml</t>
+        </is>
+      </c>
+      <c r="C5250" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="5251">
+      <c r="A5251" t="inlineStr">
+        <is>
+          <t>96126</t>
+        </is>
+      </c>
+      <c r="B5251" t="inlineStr">
+        <is>
+          <t>PRESENTE NATIVA SPA QUINOA</t>
+        </is>
+      </c>
+      <c r="C5251" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5252">
+      <c r="A5252" t="inlineStr">
+        <is>
+          <t>96701</t>
+        </is>
+      </c>
+      <c r="B5252" t="inlineStr">
+        <is>
+          <t>PRESENTE CASA 214 FIGO MAGNÍFICO</t>
+        </is>
+      </c>
+      <c r="C5252" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5253">
+      <c r="A5253" t="inlineStr">
+        <is>
+          <t>94389</t>
+        </is>
+      </c>
+      <c r="B5253" t="inlineStr">
+        <is>
+          <t>PAPEL SEDA BOTI INSTIT 2025 UNIT</t>
+        </is>
+      </c>
+      <c r="C5253" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5254">
+      <c r="A5254" t="inlineStr">
+        <is>
+          <t>88623</t>
+        </is>
+      </c>
+      <c r="B5254" t="inlineStr">
+        <is>
+          <t>OUI LOC DES HID CPO LAM V2 400ml</t>
+        </is>
+      </c>
+      <c r="C5254" t="inlineStr">
+        <is>
+          <t>O.U.I</t>
+        </is>
+      </c>
+    </row>
+    <row r="5255">
+      <c r="A5255" t="inlineStr">
+        <is>
+          <t>52665</t>
+        </is>
+      </c>
+      <c r="B5255" t="inlineStr">
+        <is>
+          <t>NSPA LOC DES HID CPO F/LOT 250ml</t>
+        </is>
+      </c>
+      <c r="C5255" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5256">
+      <c r="A5256" t="inlineStr">
+        <is>
+          <t>88083</t>
+        </is>
+      </c>
+      <c r="B5256" t="inlineStr">
+        <is>
+          <t>NSPA LOC DES HID CPO AMEIX/NEG V5 200ml</t>
+        </is>
+      </c>
+      <c r="C5256" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5257">
+      <c r="A5257" t="inlineStr">
+        <is>
+          <t>88073</t>
+        </is>
+      </c>
+      <c r="B5257" t="inlineStr">
+        <is>
+          <t>NSPA CR HID MAOS AMEIXA V6 75g</t>
+        </is>
+      </c>
+      <c r="C5257" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5258">
+      <c r="A5258" t="inlineStr">
+        <is>
+          <t>90106</t>
+        </is>
+      </c>
+      <c r="B5258" t="inlineStr">
+        <is>
+          <t>NIINA SCR LAP/LAB S/PETALS C/ENCANT 0,3g</t>
+        </is>
+      </c>
+      <c r="C5258" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5259">
+      <c r="A5259" t="inlineStr">
+        <is>
+          <t>90101</t>
+        </is>
+      </c>
+      <c r="B5259" t="inlineStr">
+        <is>
+          <t>NIINA SCR BAT SFT PETALS VER/ROMAT 3,6g</t>
+        </is>
+      </c>
+      <c r="C5259" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5260">
+      <c r="A5260" t="inlineStr">
+        <is>
+          <t>90100</t>
+        </is>
+      </c>
+      <c r="B5260" t="inlineStr">
+        <is>
+          <t>NIINA SCR BAT SFT PETALS ROS SECRET 3,6g</t>
+        </is>
+      </c>
+      <c r="C5260" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5261">
+      <c r="A5261" t="inlineStr">
+        <is>
+          <t>90093</t>
+        </is>
+      </c>
+      <c r="B5261" t="inlineStr">
+        <is>
+          <t>NIINA SCR BAT SFT PETALS ROS PETALA 3,6g</t>
+        </is>
+      </c>
+      <c r="C5261" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5262">
+      <c r="A5262" t="inlineStr">
+        <is>
+          <t>90102</t>
+        </is>
+      </c>
+      <c r="B5262" t="inlineStr">
+        <is>
+          <t>NIINA SCR BAT SFT PETALS CAS/ENCANT 3,6g</t>
+        </is>
+      </c>
+      <c r="C5262" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5263">
+      <c r="A5263" t="inlineStr">
+        <is>
+          <t>59743</t>
+        </is>
+      </c>
+      <c r="B5263" t="inlineStr">
+        <is>
+          <t>NEO DERMO CR ANT FAC 30 PRO AGE V2 50g</t>
+        </is>
+      </c>
+      <c r="C5263" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5264">
+      <c r="A5264" t="inlineStr">
+        <is>
+          <t>73811</t>
+        </is>
+      </c>
+      <c r="B5264" t="inlineStr">
+        <is>
+          <t>MEN SABONETE EM BARRA, 90g C/2</t>
+        </is>
+      </c>
+      <c r="C5264" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5265">
+      <c r="A5265" t="inlineStr">
+        <is>
+          <t>90610</t>
+        </is>
+      </c>
+      <c r="B5265" t="inlineStr">
+        <is>
+          <t>MEN SAB LIQ FAC ANTIACNE 150ml</t>
+        </is>
+      </c>
+      <c r="C5265" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5266">
+      <c r="A5266" t="inlineStr">
+        <is>
+          <t>94866</t>
+        </is>
+      </c>
+      <c r="B5266" t="inlineStr">
+        <is>
+          <t>MATCH SHAMP SCIENCE RECONST V2 300ml</t>
+        </is>
+      </c>
+      <c r="C5266" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5267">
+      <c r="A5267" t="inlineStr">
+        <is>
+          <t>88895</t>
+        </is>
+      </c>
+      <c r="B5267" t="inlineStr">
+        <is>
+          <t>LIZ D'ESSENCE DESODORANTE COLÔNIA 100 ML</t>
+        </is>
+      </c>
+      <c r="C5267" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5268">
+      <c r="A5268" t="inlineStr">
+        <is>
+          <t>90298</t>
+        </is>
+      </c>
+      <c r="B5268" t="inlineStr">
+        <is>
+          <t>LIZ D'ESSENCE CREME HIDRATANTE DESODORANTE CORPORAL, 250 g</t>
+        </is>
+      </c>
+      <c r="C5268" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5269">
+      <c r="A5269" t="inlineStr">
+        <is>
+          <t>85702</t>
+        </is>
+      </c>
+      <c r="B5269" t="inlineStr">
+        <is>
+          <t>LILY EDP V3 30ml</t>
+        </is>
+      </c>
+      <c r="C5269" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5270">
+      <c r="A5270" t="inlineStr">
+        <is>
+          <t>90237</t>
+        </is>
+      </c>
+      <c r="B5270" t="inlineStr">
+        <is>
+          <t>KIT PRESENTE ZAAD PAIS 26</t>
+        </is>
+      </c>
+      <c r="C5270" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5271">
+      <c r="A5271" t="inlineStr">
+        <is>
+          <t>90242</t>
+        </is>
+      </c>
+      <c r="B5271" t="inlineStr">
+        <is>
+          <t>KIT PRESENTE UOMINI PAIS 26</t>
+        </is>
+      </c>
+      <c r="C5271" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5272">
+      <c r="A5272" t="inlineStr">
+        <is>
+          <t>89966</t>
+        </is>
+      </c>
+      <c r="B5272" t="inlineStr">
+        <is>
+          <t>Kit Presente Quasar Vision Amor 2026</t>
+        </is>
+      </c>
+      <c r="C5272" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5273">
+      <c r="A5273" t="inlineStr">
+        <is>
+          <t>90247</t>
+        </is>
+      </c>
+      <c r="B5273" t="inlineStr">
+        <is>
+          <t>KIT PRESENTE QUASAR BLUE PAIS 26</t>
+        </is>
+      </c>
+      <c r="C5273" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5274">
+      <c r="A5274" t="inlineStr">
+        <is>
+          <t>90241</t>
+        </is>
+      </c>
+      <c r="B5274" t="inlineStr">
+        <is>
+          <t>KIT PRESENTE PORTINARI PAIS 26</t>
+        </is>
+      </c>
+      <c r="C5274" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5275">
+      <c r="A5275" t="inlineStr">
+        <is>
+          <t>94440</t>
+        </is>
+      </c>
+      <c r="B5275" t="inlineStr">
+        <is>
+          <t>KIT PRESENTE OBSESSÃO POR BAUNILHA</t>
+        </is>
+      </c>
+      <c r="C5275" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5276">
+      <c r="A5276" t="inlineStr">
+        <is>
+          <t>89970</t>
+        </is>
+      </c>
+      <c r="B5276" t="inlineStr">
+        <is>
+          <t>Kit Presente Nativa Spa Orquídea Lumière Amor 2026</t>
+        </is>
+      </c>
+      <c r="C5276" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5277">
+      <c r="A5277" t="inlineStr">
+        <is>
+          <t>89958</t>
+        </is>
+      </c>
+      <c r="B5277" t="inlineStr">
+        <is>
+          <t>Kit Presente Malbec X Amor 2026</t>
+        </is>
+      </c>
+      <c r="C5277" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5278">
+      <c r="A5278" t="inlineStr">
+        <is>
+          <t>90238</t>
+        </is>
+      </c>
+      <c r="B5278" t="inlineStr">
+        <is>
+          <t>KIT PRESENTE MALBEC PAIS 26</t>
+        </is>
+      </c>
+      <c r="C5278" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5279">
+      <c r="A5279" t="inlineStr">
+        <is>
+          <t>90240</t>
+        </is>
+      </c>
+      <c r="B5279" t="inlineStr">
+        <is>
+          <t>KIT PRESENTE MALBEC ICON PAIS 26</t>
+        </is>
+      </c>
+      <c r="C5279" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5280">
+      <c r="A5280" t="inlineStr">
+        <is>
+          <t>89960</t>
+        </is>
+      </c>
+      <c r="B5280" t="inlineStr">
+        <is>
+          <t>Kit Presente L'eau de Lily Amor 2026</t>
+        </is>
+      </c>
+      <c r="C5280" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5281">
+      <c r="A5281" t="inlineStr">
+        <is>
+          <t>90253</t>
+        </is>
+      </c>
+      <c r="B5281" t="inlineStr">
+        <is>
+          <t>KIT PRESENTE KISS ME NOW</t>
+        </is>
+      </c>
+      <c r="C5281" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5282">
+      <c r="A5282" t="inlineStr">
+        <is>
+          <t>90820</t>
+        </is>
+      </c>
+      <c r="B5282" t="inlineStr">
+        <is>
+          <t>KIT PRESENTE IMENSI ALIVE</t>
+        </is>
+      </c>
+      <c r="C5282" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5283">
+      <c r="A5283" t="inlineStr">
+        <is>
+          <t>89957</t>
+        </is>
+      </c>
+      <c r="B5283" t="inlineStr">
+        <is>
+          <t>Kit Presente Her Code Climax Amor 2026</t>
+        </is>
+      </c>
+      <c r="C5283" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5284">
+      <c r="A5284" t="inlineStr">
+        <is>
+          <t>89959</t>
+        </is>
+      </c>
+      <c r="B5284" t="inlineStr">
+        <is>
+          <t>Kit Presente Floratta Red Passion Amor 2026</t>
+        </is>
+      </c>
+      <c r="C5284" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5285">
+      <c r="A5285" t="inlineStr">
+        <is>
+          <t>89963</t>
+        </is>
+      </c>
+      <c r="B5285" t="inlineStr">
+        <is>
+          <t>Kit Presente Floratta Red Amor 2026</t>
+        </is>
+      </c>
+      <c r="C5285" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5286">
+      <c r="A5286" t="inlineStr">
+        <is>
+          <t>90250</t>
+        </is>
+      </c>
+      <c r="B5286" t="inlineStr">
+        <is>
+          <t>KIT PRESENTE EGEO ORIGINAL PAIS 26</t>
+        </is>
+      </c>
+      <c r="C5286" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5287">
+      <c r="A5287" t="inlineStr">
+        <is>
+          <t>89964</t>
+        </is>
+      </c>
+      <c r="B5287" t="inlineStr">
+        <is>
+          <t>Kit Presente Egeo Dolce Amor 2026</t>
+        </is>
+      </c>
+      <c r="C5287" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5288">
+      <c r="A5288" t="inlineStr">
+        <is>
+          <t>89965</t>
+        </is>
+      </c>
+      <c r="B5288" t="inlineStr">
+        <is>
+          <t>Kit Presente Egeo Bomb Black Amor 2026</t>
+        </is>
+      </c>
+      <c r="C5288" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5289">
+      <c r="A5289" t="inlineStr">
+        <is>
+          <t>89969</t>
+        </is>
+      </c>
+      <c r="B5289" t="inlineStr">
+        <is>
+          <t>Kit Presente Cuide-se Bem Amoruda Amor 2026</t>
+        </is>
+      </c>
+      <c r="C5289" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5290">
+      <c r="A5290" t="inlineStr">
+        <is>
+          <t>94630</t>
+        </is>
+      </c>
+      <c r="B5290" t="inlineStr">
+        <is>
+          <t>KIT PRESENTE CONNEXION PAIS 26</t>
+        </is>
+      </c>
+      <c r="C5290" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5291">
+      <c r="A5291" t="inlineStr">
+        <is>
+          <t>89962</t>
+        </is>
+      </c>
+      <c r="B5291" t="inlineStr">
+        <is>
+          <t>Kit Presente Coffee Woman Sedution Amor 2026</t>
+        </is>
+      </c>
+      <c r="C5291" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5292">
+      <c r="A5292" t="inlineStr">
+        <is>
+          <t>94441</t>
+        </is>
+      </c>
+      <c r="B5292" t="inlineStr">
+        <is>
+          <t>KIT PRESENTE CLUB 6</t>
+        </is>
+      </c>
+      <c r="C5292" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5293">
+      <c r="A5293" t="inlineStr">
+        <is>
+          <t>90243</t>
+        </is>
+      </c>
+      <c r="B5293" t="inlineStr">
+        <is>
+          <t>KIT PRESENTE CLASH PAIS 26</t>
+        </is>
+      </c>
+      <c r="C5293" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5294">
+      <c r="A5294" t="inlineStr">
+        <is>
+          <t>90852</t>
+        </is>
+      </c>
+      <c r="B5294" t="inlineStr">
+        <is>
+          <t>KIT PRESENTE CELEBRE SUA FORÇA PAIS 26</t>
+        </is>
+      </c>
+      <c r="C5294" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5295">
+      <c r="A5295" t="inlineStr">
+        <is>
+          <t>89967</t>
+        </is>
+      </c>
+      <c r="B5295" t="inlineStr">
+        <is>
+          <t>Kit Presente Celebre Agora MAsculino Amor 2026</t>
+        </is>
+      </c>
+      <c r="C5295" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5296">
+      <c r="A5296" t="inlineStr">
+        <is>
+          <t>89968</t>
+        </is>
+      </c>
+      <c r="B5296" t="inlineStr">
+        <is>
+          <t>Kit Presente Celebre Agora Feminino Amor 2026</t>
+        </is>
+      </c>
+      <c r="C5296" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5297">
+      <c r="A5297" t="inlineStr">
+        <is>
+          <t>89961</t>
+        </is>
+      </c>
+      <c r="B5297" t="inlineStr">
+        <is>
+          <t>Kit Presente Botica 214 Dark Mint Amor 2026</t>
+        </is>
+      </c>
+      <c r="C5297" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5298">
+      <c r="A5298" t="inlineStr">
+        <is>
+          <t>90255</t>
+        </is>
+      </c>
+      <c r="B5298" t="inlineStr">
+        <is>
+          <t>KIT PRESENTE BODY SPRAY IMPRESSION E INTENTION</t>
+        </is>
+      </c>
+      <c r="C5298" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5299">
+      <c r="A5299" t="inlineStr">
+        <is>
+          <t>90239</t>
+        </is>
+      </c>
+      <c r="B5299" t="inlineStr">
+        <is>
+          <t>KIT PRESENTE ARBO PAIS 26</t>
+        </is>
+      </c>
+      <c r="C5299" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5300">
+      <c r="A5300" t="inlineStr">
+        <is>
+          <t>90902</t>
+        </is>
+      </c>
+      <c r="B5300" t="inlineStr">
+        <is>
+          <t>KIT DR BOTICA MAGICO TEATRO BONECOS V2</t>
+        </is>
+      </c>
+      <c r="C5300" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5301">
+      <c r="A5301" t="inlineStr">
+        <is>
+          <t>91302</t>
+        </is>
+      </c>
+      <c r="B5301" t="inlineStr">
+        <is>
+          <t>INSTANCE DES COL FR/VERM 200ml</t>
+        </is>
+      </c>
+      <c r="C5301" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5302">
+      <c r="A5302" t="inlineStr">
+        <is>
+          <t>95619</t>
+        </is>
+      </c>
+      <c r="B5302" t="inlineStr">
+        <is>
+          <t>INSTANCE D/COL BDY/SPL MOR/IRR V2 200ml</t>
+        </is>
+      </c>
+      <c r="C5302" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5303">
+      <c r="A5303" t="inlineStr">
+        <is>
+          <t>95353</t>
+        </is>
+      </c>
+      <c r="B5303" t="inlineStr">
+        <is>
+          <t>INSTANCE CR DES H CP AMEIX/PR 180ml RPCK</t>
+        </is>
+      </c>
+      <c r="C5303" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5304">
+      <c r="A5304" t="inlineStr">
+        <is>
+          <t>85955</t>
+        </is>
+      </c>
+      <c r="B5304" t="inlineStr">
+        <is>
+          <t>INSTANCE CALDA BNH AMEIX/PRAL RPKC 180ml</t>
+        </is>
+      </c>
+      <c r="C5304" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5305">
+      <c r="A5305" t="inlineStr">
+        <is>
+          <t>84874</t>
+        </is>
+      </c>
+      <c r="B5305" t="inlineStr">
+        <is>
+          <t>EUD MAKE BAT MATE K/M ROS/UNICO V4 3,7g</t>
+        </is>
+      </c>
+      <c r="C5305" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5306">
+      <c r="A5306" t="inlineStr">
+        <is>
+          <t>89767</t>
+        </is>
+      </c>
+      <c r="B5306" t="inlineStr">
+        <is>
+          <t>EUD DES COL VELVET SOUL 100ml</t>
+        </is>
+      </c>
+      <c r="C5306" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5307">
+      <c r="A5307" t="inlineStr">
+        <is>
+          <t>90141</t>
+        </is>
+      </c>
+      <c r="B5307" t="inlineStr">
+        <is>
+          <t>EUD DES BDY SPR VELVET SOUL 100ml</t>
+        </is>
+      </c>
+      <c r="C5307" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5308">
+      <c r="A5308" t="inlineStr">
+        <is>
+          <t>52654</t>
+        </is>
+      </c>
+      <c r="B5308" t="inlineStr">
+        <is>
+          <t>ESTJ NSPA QUINOA REG/21 V2</t>
+        </is>
+      </c>
+      <c r="C5308" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5309">
+      <c r="A5309" t="inlineStr">
+        <is>
+          <t>94400</t>
+        </is>
+      </c>
+      <c r="B5309" t="inlineStr">
+        <is>
+          <t>ESTJ CASA 214 FIGO MAGNIFICO</t>
+        </is>
+      </c>
+      <c r="C5309" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5310">
+      <c r="A5310" t="inlineStr">
+        <is>
+          <t>81264</t>
+        </is>
+      </c>
+      <c r="B5310" t="inlineStr">
+        <is>
+          <t>DEM CBEM DES COL BDY SPLSH BEND/CACT 4ml</t>
+        </is>
+      </c>
+      <c r="C5310" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5311">
+      <c r="A5311" t="inlineStr">
+        <is>
+          <t>85654</t>
+        </is>
+      </c>
+      <c r="B5311" t="inlineStr">
+        <is>
+          <t>DEM BOTICA 214 EDP ARAB/OAS FL/FRUT 4ml</t>
+        </is>
+      </c>
+      <c r="C5311" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5312">
+      <c r="A5312" t="inlineStr">
+        <is>
+          <t>89397</t>
+        </is>
+      </c>
+      <c r="B5312" t="inlineStr">
+        <is>
+          <t>CX PRESENTE G BOT INST/25 VDA</t>
+        </is>
+      </c>
+      <c r="C5312" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5313">
+      <c r="A5313" t="inlineStr">
+        <is>
+          <t>98403</t>
+        </is>
+      </c>
+      <c r="B5313" t="inlineStr">
+        <is>
+          <t>COMBO SIAGE NUTRI DIAMOND (5 itens)</t>
+        </is>
+      </c>
+      <c r="C5313" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5314">
+      <c r="A5314" t="inlineStr">
+        <is>
+          <t>96462</t>
+        </is>
+      </c>
+      <c r="B5314" t="inlineStr">
+        <is>
+          <t>COMBO SIAGE NUTRI DIAMOND (3 itens)</t>
+        </is>
+      </c>
+      <c r="C5314" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5315">
+      <c r="A5315" t="inlineStr">
+        <is>
+          <t>97991</t>
+        </is>
+      </c>
+      <c r="B5315" t="inlineStr">
+        <is>
+          <t>COMBO SIAGE NUTRI DIAMOND (2 itens)</t>
+        </is>
+      </c>
+      <c r="C5315" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5316">
+      <c r="A5316" t="inlineStr">
+        <is>
+          <t>97852</t>
+        </is>
+      </c>
+      <c r="B5316" t="inlineStr">
+        <is>
+          <t>Combo Siage Acelera o Crescimento (4 Itens)</t>
+        </is>
+      </c>
+      <c r="C5316" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5317">
+      <c r="A5317" t="inlineStr">
+        <is>
+          <t>98399</t>
+        </is>
+      </c>
+      <c r="B5317" t="inlineStr">
+        <is>
+          <t>COMBO MATCH</t>
+        </is>
+      </c>
+      <c r="C5317" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5318">
+      <c r="A5318" t="inlineStr">
+        <is>
+          <t>98196</t>
+        </is>
+      </c>
+      <c r="B5318" t="inlineStr">
+        <is>
+          <t>COMBO LILY ( 2 ITENS)</t>
+        </is>
+      </c>
+      <c r="C5318" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5319">
+      <c r="A5319" t="inlineStr">
+        <is>
+          <t>98400</t>
+        </is>
+      </c>
+      <c r="B5319" t="inlineStr">
+        <is>
+          <t>COMB SOPHIE SHIMMER</t>
+        </is>
+      </c>
+      <c r="C5319" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5320">
+      <c r="A5320" t="inlineStr">
+        <is>
+          <t>96468</t>
+        </is>
+      </c>
+      <c r="B5320" t="inlineStr">
+        <is>
+          <t>COMB SIAGE VOLUME IMEDIATO 02</t>
+        </is>
+      </c>
+      <c r="C5320" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5321">
+      <c r="A5321" t="inlineStr">
+        <is>
+          <t>96461</t>
+        </is>
+      </c>
+      <c r="B5321" t="inlineStr">
+        <is>
+          <t>COMB SIAGE PRO CRONOLOGY CURVAS 03</t>
+        </is>
+      </c>
+      <c r="C5321" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5322">
+      <c r="A5322" t="inlineStr">
+        <is>
+          <t>96078</t>
+        </is>
+      </c>
+      <c r="B5322" t="inlineStr">
+        <is>
+          <t>COMB QDB 03 MAES/26</t>
+        </is>
+      </c>
+      <c r="C5322" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="5323">
+      <c r="A5323" t="inlineStr">
+        <is>
+          <t>96374</t>
+        </is>
+      </c>
+      <c r="B5323" t="inlineStr">
+        <is>
+          <t>COMB OUI SCAPIN 245 02 MAES/26</t>
+        </is>
+      </c>
+      <c r="C5323" t="inlineStr">
+        <is>
+          <t>O.U.I</t>
+        </is>
+      </c>
+    </row>
+    <row r="5324">
+      <c r="A5324" t="inlineStr">
+        <is>
+          <t>95916</t>
+        </is>
+      </c>
+      <c r="B5324" t="inlineStr">
+        <is>
+          <t>COMB LA VICTORIE AMOR/26</t>
+        </is>
+      </c>
+      <c r="C5324" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5325">
+      <c r="A5325" t="inlineStr">
+        <is>
+          <t>95696</t>
+        </is>
+      </c>
+      <c r="B5325" t="inlineStr">
+        <is>
+          <t>COMB EUDORA H MARINE NAM/26</t>
+        </is>
+      </c>
+      <c r="C5325" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5326">
+      <c r="A5326" t="inlineStr">
+        <is>
+          <t>96819</t>
+        </is>
+      </c>
+      <c r="B5326" t="inlineStr">
+        <is>
+          <t>COMB EUD VELVET SOUL 02</t>
+        </is>
+      </c>
+      <c r="C5326" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5327">
+      <c r="A5327" t="inlineStr">
+        <is>
+          <t>96818</t>
+        </is>
+      </c>
+      <c r="B5327" t="inlineStr">
+        <is>
+          <t>COMB EUD VELVET SOUL</t>
+        </is>
+      </c>
+      <c r="C5327" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5328">
+      <c r="A5328" t="inlineStr">
+        <is>
+          <t>95695</t>
+        </is>
+      </c>
+      <c r="B5328" t="inlineStr">
+        <is>
+          <t>COMB EUD ROUGE NAM/26</t>
+        </is>
+      </c>
+      <c r="C5328" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5329">
+      <c r="A5329" t="inlineStr">
+        <is>
+          <t>97594</t>
+        </is>
+      </c>
+      <c r="B5329" t="inlineStr">
+        <is>
+          <t>COMB DIVA SUPREMA AMOR/26</t>
+        </is>
+      </c>
+      <c r="C5329" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5330">
+      <c r="A5330" t="inlineStr">
+        <is>
+          <t>95913</t>
+        </is>
+      </c>
+      <c r="B5330" t="inlineStr">
+        <is>
+          <t>COMB CLUB 6 CASSINO AMOR/26</t>
+        </is>
+      </c>
+      <c r="C5330" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5331">
+      <c r="A5331" t="inlineStr">
+        <is>
+          <t>98401</t>
+        </is>
+      </c>
+      <c r="B5331" t="inlineStr">
+        <is>
+          <t>COMB CBEM DES COL BODY SPLASH 1</t>
+        </is>
+      </c>
+      <c r="C5331" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5332">
+      <c r="A5332" t="inlineStr">
+        <is>
+          <t>98402</t>
+        </is>
+      </c>
+      <c r="B5332" t="inlineStr">
+        <is>
+          <t>COMB CBEM BODY SPLASH 2</t>
+        </is>
+      </c>
+      <c r="C5332" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5333">
+      <c r="A5333" t="inlineStr">
+        <is>
+          <t>98191</t>
+        </is>
+      </c>
+      <c r="B5333" t="inlineStr">
+        <is>
+          <t>COMB BOTICA 214 ARABIAN OASIS (4 itens)</t>
+        </is>
+      </c>
+      <c r="C5333" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5334">
+      <c r="A5334" t="inlineStr">
+        <is>
+          <t>94676</t>
+        </is>
+      </c>
+      <c r="B5334" t="inlineStr">
+        <is>
+          <t>CBEM ESF FAC FEIRA MORANGO V2 100g</t>
+        </is>
+      </c>
+      <c r="C5334" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5335">
+      <c r="A5335" t="inlineStr">
+        <is>
+          <t>85645</t>
+        </is>
+      </c>
+      <c r="B5335" t="inlineStr">
+        <is>
+          <t>BOTICA 214 ARABIAN OASIS FOUGÈRE AMBARADO EAU DE PARFUM, 90ml</t>
+        </is>
+      </c>
+      <c r="C5335" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5336">
+      <c r="A5336" t="inlineStr">
+        <is>
+          <t>85644</t>
+        </is>
+      </c>
+      <c r="B5336" t="inlineStr">
+        <is>
+          <t>BOTICA 214 ARABIAN OASIS FLORAL FRUTAL EAU DE PARFUM, 75ml</t>
+        </is>
+      </c>
+      <c r="C5336" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
         </is>
       </c>
     </row>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5336"/>
+  <dimension ref="A1:C5358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91130,6 +91130,380 @@
       <c r="C5336" t="inlineStr">
         <is>
           <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5337">
+      <c r="A5337" t="inlineStr">
+        <is>
+          <t>97395</t>
+        </is>
+      </c>
+      <c r="B5337" t="inlineStr">
+        <is>
+          <t>COMB CLUB 6 PRESTIGE PAIS/26</t>
+        </is>
+      </c>
+      <c r="C5337" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5338">
+      <c r="A5338" t="inlineStr">
+        <is>
+          <t>87938</t>
+        </is>
+      </c>
+      <c r="B5338" t="inlineStr">
+        <is>
+          <t>CLUB 6 EAU DE PARFUM, 95 ml</t>
+        </is>
+      </c>
+      <c r="C5338" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5339">
+      <c r="A5339" t="inlineStr">
+        <is>
+          <t>96809</t>
+        </is>
+      </c>
+      <c r="B5339" t="inlineStr">
+        <is>
+          <t>COMB IMPRESSION PAIS/26</t>
+        </is>
+      </c>
+      <c r="C5339" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5340">
+      <c r="A5340" t="inlineStr">
+        <is>
+          <t>94163</t>
+        </is>
+      </c>
+      <c r="B5340" t="inlineStr">
+        <is>
+          <t>NIINA SCRT PLT SOMBRAS SOFT PETALS 10g</t>
+        </is>
+      </c>
+      <c r="C5340" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5341">
+      <c r="A5341" t="inlineStr">
+        <is>
+          <t>96805</t>
+        </is>
+      </c>
+      <c r="B5341" t="inlineStr">
+        <is>
+          <t>COMB EUDORA H ACQUA PAIS/26</t>
+        </is>
+      </c>
+      <c r="C5341" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5342">
+      <c r="A5342" t="inlineStr">
+        <is>
+          <t>98542</t>
+        </is>
+      </c>
+      <c r="B5342" t="inlineStr">
+        <is>
+          <t>COMB NIINA SECRETS SOFT PETALS 03</t>
+        </is>
+      </c>
+      <c r="C5342" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5343">
+      <c r="A5343" t="inlineStr">
+        <is>
+          <t>96804</t>
+        </is>
+      </c>
+      <c r="B5343" t="inlineStr">
+        <is>
+          <t>COMB EUD SENSUAL VELVET PAIS/26</t>
+        </is>
+      </c>
+      <c r="C5343" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5344">
+      <c r="A5344" t="inlineStr">
+        <is>
+          <t>95312</t>
+        </is>
+      </c>
+      <c r="B5344" t="inlineStr">
+        <is>
+          <t>NIINA SCR BAT SFT PETALS MAR/AVELUD 3,6g</t>
+        </is>
+      </c>
+      <c r="C5344" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5345">
+      <c r="A5345" t="inlineStr">
+        <is>
+          <t>84872</t>
+        </is>
+      </c>
+      <c r="B5345" t="inlineStr">
+        <is>
+          <t>EUD MAKE BATOM MATTE KISS ME NUDE REALCE</t>
+        </is>
+      </c>
+      <c r="C5345" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5346">
+      <c r="A5346" t="inlineStr">
+        <is>
+          <t>90103</t>
+        </is>
+      </c>
+      <c r="B5346" t="inlineStr">
+        <is>
+          <t>NIINA SCR LAP/LAB S/PETALS R/PETALA 0,3g</t>
+        </is>
+      </c>
+      <c r="C5346" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5347">
+      <c r="A5347" t="inlineStr">
+        <is>
+          <t>90105</t>
+        </is>
+      </c>
+      <c r="B5347" t="inlineStr">
+        <is>
+          <t>NIINA SCR LAP/LAB S/PETALS VER/ROM 0,3g</t>
+        </is>
+      </c>
+      <c r="C5347" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5348">
+      <c r="A5348" t="inlineStr">
+        <is>
+          <t>95313</t>
+        </is>
+      </c>
+      <c r="B5348" t="inlineStr">
+        <is>
+          <t>NIINA SCR LAP/LAB S/PETALS MAR/AVEL 0,3g</t>
+        </is>
+      </c>
+      <c r="C5348" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5349">
+      <c r="A5349" t="inlineStr">
+        <is>
+          <t>88688</t>
+        </is>
+      </c>
+      <c r="B5349" t="inlineStr">
+        <is>
+          <t>CBEM LOC DES HID CPO NUVEM N/FORM 400ml</t>
+        </is>
+      </c>
+      <c r="C5349" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5350">
+      <c r="A5350" t="inlineStr">
+        <is>
+          <t>86798</t>
+        </is>
+      </c>
+      <c r="B5350" t="inlineStr">
+        <is>
+          <t>NSPA CR PARFUMEE CPO AMEIXA 200g</t>
+        </is>
+      </c>
+      <c r="C5350" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5351">
+      <c r="A5351" t="inlineStr">
+        <is>
+          <t>95648</t>
+        </is>
+      </c>
+      <c r="B5351" t="inlineStr">
+        <is>
+          <t>KIT PRESENTE COFFEE MAN ADDICTIVE PAIS 26</t>
+        </is>
+      </c>
+      <c r="C5351" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5352">
+      <c r="A5352" t="inlineStr">
+        <is>
+          <t>90249</t>
+        </is>
+      </c>
+      <c r="B5352" t="inlineStr">
+        <is>
+          <t>KIT PRESENTE MALBEC B/SPRAY PAIS 26</t>
+        </is>
+      </c>
+      <c r="C5352" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5353">
+      <c r="A5353" t="inlineStr">
+        <is>
+          <t>94499</t>
+        </is>
+      </c>
+      <c r="B5353" t="inlineStr">
+        <is>
+          <t>CBEM SAB BARRA PESSEGURA V3 4x80g</t>
+        </is>
+      </c>
+      <c r="C5353" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5354">
+      <c r="A5354" t="inlineStr">
+        <is>
+          <t>88130</t>
+        </is>
+      </c>
+      <c r="B5354" t="inlineStr">
+        <is>
+          <t>HER CODE BODY SPLASH DESODORANTE COLONIA, 200ml</t>
+        </is>
+      </c>
+      <c r="C5354" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5355">
+      <c r="A5355" t="inlineStr">
+        <is>
+          <t>88971</t>
+        </is>
+      </c>
+      <c r="B5355" t="inlineStr">
+        <is>
+          <t>LIZ DES COL D ESSENCE PRM 10ml</t>
+        </is>
+      </c>
+      <c r="C5355" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5356">
+      <c r="A5356" t="inlineStr">
+        <is>
+          <t>85653</t>
+        </is>
+      </c>
+      <c r="B5356" t="inlineStr">
+        <is>
+          <t>DEM BOTICA 214 EDP ARAB/OAS FOUG/AMB 4ml</t>
+        </is>
+      </c>
+      <c r="C5356" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5357">
+      <c r="A5357" t="inlineStr">
+        <is>
+          <t>88897</t>
+        </is>
+      </c>
+      <c r="B5357" t="inlineStr">
+        <is>
+          <t>CJ FLAC LIZ DES COL D ESSENCE 5x1ml</t>
+        </is>
+      </c>
+      <c r="C5357" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5358">
+      <c r="A5358" t="inlineStr">
+        <is>
+          <t>86396</t>
+        </is>
+      </c>
+      <c r="B5358" t="inlineStr">
+        <is>
+          <t>O.U.i Desir Parisien 750 Eau de Parfum Pour Femme 75ml</t>
+        </is>
+      </c>
+      <c r="C5358" t="inlineStr">
+        <is>
+          <t>O.U.I</t>
         </is>
       </c>
     </row>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -78748,7 +78748,7 @@
       </c>
       <c r="C4607" s="1" t="inlineStr">
         <is>
-          <t>OBOTICÁRIO</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
@@ -78935,7 +78935,7 @@
       </c>
       <c r="C4618" s="1" t="inlineStr">
         <is>
-          <t>OBOTICÁRIO</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
@@ -79921,7 +79921,7 @@
       </c>
       <c r="C4676" s="1" t="inlineStr">
         <is>
-          <t>OBOTICÁRIO</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
@@ -79955,7 +79955,7 @@
       </c>
       <c r="C4678" s="1" t="inlineStr">
         <is>
-          <t>OBOTICÁRIO</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
@@ -82935,7 +82935,7 @@
       </c>
       <c r="C4854" s="1" t="inlineStr">
         <is>
-          <t>OBOTICÁRIO</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
@@ -83003,7 +83003,7 @@
       </c>
       <c r="C4858" s="1" t="inlineStr">
         <is>
-          <t>OBOTICÁRIO</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
@@ -83190,7 +83190,7 @@
       </c>
       <c r="C4869" s="1" t="inlineStr">
         <is>
-          <t>OBOTICÁRIO</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -82799,7 +82799,7 @@
       </c>
       <c r="C4846" s="1" t="inlineStr">
         <is>
-          <t>EUD</t>
+          <t>oBoticário</t>
         </is>
       </c>
     </row>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5358"/>
+  <dimension ref="A1:C5360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91504,6 +91504,40 @@
       <c r="C5358" t="inlineStr">
         <is>
           <t>O.U.I</t>
+        </is>
+      </c>
+    </row>
+    <row r="5359">
+      <c r="A5359" t="inlineStr">
+        <is>
+          <t>94200</t>
+        </is>
+      </c>
+      <c r="B5359" t="inlineStr">
+        <is>
+          <t>MATCH MASC C H 2AB 3AB CIEN/CURV V2 350g</t>
+        </is>
+      </c>
+      <c r="C5359" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5360">
+      <c r="A5360" t="inlineStr">
+        <is>
+          <t>89784</t>
+        </is>
+      </c>
+      <c r="B5360" t="inlineStr">
+        <is>
+          <t>MALBEC COND TRAT ANTICASPA CUID V4 250ml</t>
+        </is>
+      </c>
+      <c r="C5360" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
         </is>
       </c>
     </row>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -82799,7 +82799,7 @@
       </c>
       <c r="C4846" s="1" t="inlineStr">
         <is>
-          <t>oBoticário</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5360"/>
+  <dimension ref="A1:C5361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91538,6 +91538,23 @@
       <c r="C5360" t="inlineStr">
         <is>
           <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="5361">
+      <c r="A5361" t="inlineStr">
+        <is>
+          <t>97446</t>
+        </is>
+      </c>
+      <c r="B5361" t="inlineStr">
+        <is>
+          <t>COMB SIAGE CAUTERIZACAO/FIOS 04</t>
+        </is>
+      </c>
+      <c r="C5361" t="inlineStr">
+        <is>
+          <t>Eudora</t>
         </is>
       </c>
     </row>

--- a/data/estoqueplanilha.xlsx
+++ b/data/estoqueplanilha.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5361"/>
+  <dimension ref="A1:C5365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91555,6 +91555,74 @@
       <c r="C5361" t="inlineStr">
         <is>
           <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5362">
+      <c r="A5362" t="inlineStr">
+        <is>
+          <t>86534</t>
+        </is>
+      </c>
+      <c r="B5362" t="inlineStr">
+        <is>
+          <t>EUD MAKE BAT HID K/M VERM/ARRASO 3,7g</t>
+        </is>
+      </c>
+      <c r="C5362" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5363">
+      <c r="A5363" t="inlineStr">
+        <is>
+          <t>97462</t>
+        </is>
+      </c>
+      <c r="B5363" t="inlineStr">
+        <is>
+          <t>COMB PULSE INTENSE</t>
+        </is>
+      </c>
+      <c r="C5363" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5364">
+      <c r="A5364" t="inlineStr">
+        <is>
+          <t>96806</t>
+        </is>
+      </c>
+      <c r="B5364" t="inlineStr">
+        <is>
+          <t>COMB VOLPE PAIS/26</t>
+        </is>
+      </c>
+      <c r="C5364" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5365">
+      <c r="A5365" t="inlineStr">
+        <is>
+          <t>96222</t>
+        </is>
+      </c>
+      <c r="B5365" t="inlineStr">
+        <is>
+          <t>COMB HER CODE AMOR/26</t>
+        </is>
+      </c>
+      <c r="C5365" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
         </is>
       </c>
     </row>
